--- a/data/staging/source/1.6GreenHouseGas2026.xlsx
+++ b/data/staging/source/1.6GreenHouseGas2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://maejo365-my.sharepoint.com/personal/researchmju_mju_ac_th/Documents/RAE-Document-Center/07-GreenOffice/Resource/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="329" documentId="8_{51FF4738-6B3F-47B1-A08A-128A11E35662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7399B49D-A9F7-4D1B-A8E7-2FFBC52C00B4}"/>
+  <xr:revisionPtr revIDLastSave="367" documentId="8_{51FF4738-6B3F-47B1-A08A-128A11E35662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67D6C9CD-74FD-4BC0-9C32-216D86537687}"/>
   <bookViews>
     <workbookView xWindow="23880" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="898" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -624,7 +624,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="294">
   <si>
     <t>แบบฟอร์ม 1.5(1)</t>
   </si>
@@ -950,46 +950,7 @@
     <t>รายละเอียด :</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="20"/>
-        <color rgb="FF000000"/>
-        <rFont val="Cordia New"/>
-      </rPr>
-      <t xml:space="preserve">ปริมาณการปล่อยก๊าซเรือนกระจกในเดือนมกราคม 2569 เพิ่มขึ้นเมื่อเปรียบเทียบกับช่วงเวลาเดียวกันของปี 2568 จำนวน </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="20"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Cordia New"/>
-      </rPr>
-      <t>4,552.27</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="20"/>
-        <color rgb="FF000000"/>
-        <rFont val="Cordia New"/>
-      </rPr>
-      <t xml:space="preserve"> kgCO2 หรือเพิ่มขึ้น เท่ากับ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="20"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Cordia New"/>
-      </rPr>
-      <t>30.27</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="20"/>
-        <color rgb="FF000000"/>
-        <rFont val="Cordia New"/>
-      </rPr>
-      <t>%</t>
-    </r>
+    <t>ปริมาณการปล่อยก๊าซเรือนกระจกในเดือนมกราคม 2569 เพิ่มขึ้นเมื่อเปรียบเทียบกับช่วงเวลาเดียวกันของปี 2568 จำนวน 5,426.51 kgCO2 หรือเพิ่มขึ้น เท่ากับ 50.71%</t>
   </si>
   <si>
     <r>
@@ -1003,10 +964,10 @@
     <r>
       <rPr>
         <sz val="20"/>
-        <color rgb="FFFF0000"/>
+        <color rgb="FF000000"/>
         <rFont val="Cordia New"/>
       </rPr>
-      <t>2,306.43</t>
+      <t>2,473.08</t>
     </r>
     <r>
       <rPr>
@@ -1019,10 +980,10 @@
     <r>
       <rPr>
         <sz val="20"/>
-        <color rgb="FFFF0000"/>
+        <color rgb="FF000000"/>
         <rFont val="Cordia New"/>
       </rPr>
-      <t>9.12</t>
+      <t>11.66</t>
     </r>
     <r>
       <rPr>
@@ -1037,13 +998,7 @@
     <t>วิเคราะห์สาเหตุ :</t>
   </si>
   <si>
-    <t>บุคลากรเกิดความตื่นตัวจากการเข้าร่วมโครงการสำนักงานสีเขียวเป็นปีแรก ประกอบกับมีการรณรงค์อย่างต่อเนื่อง ทำให้บุคลากรให้ความร่วมมือในการควบคุมการใช้พลังงาน ทรัพยากร และของเสีย อย่างพร้อมเพรียงกัน</t>
-  </si>
-  <si>
     <t>แนวทางจัดการ :</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
   <si>
     <t xml:space="preserve">เดือนกุมภาพันธ์ 2569     </t>
@@ -1052,46 +1007,7 @@
     <t xml:space="preserve">เดือนสิงหาคม 2569     </t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="20"/>
-        <color rgb="FF000000"/>
-        <rFont val="Cordia New"/>
-      </rPr>
-      <t xml:space="preserve">ปริมาณการปล่อยก๊าซเรือนกระจกในเดือนกุมภาพันธ์ 2569 เพิ่มขึ้นเมื่อเปรียบเทียบกับช่วงเวลาเดียวกันของปี 2568 จำนวน </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="20"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Cordia New"/>
-      </rPr>
-      <t>2,204.30</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="20"/>
-        <color rgb="FF000000"/>
-        <rFont val="Cordia New"/>
-      </rPr>
-      <t xml:space="preserve"> kgCO2 หรือเพิ่มขึ้น เท่ากับ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="20"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Cordia New"/>
-      </rPr>
-      <t>13.66</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="20"/>
-        <color rgb="FF000000"/>
-        <rFont val="Cordia New"/>
-      </rPr>
-      <t>%</t>
-    </r>
+    <t>ปริมาณการปล่อยก๊าซเรือนกระจกในเดือนกุมภาพันธ์ 2569 เพิ่มขึ้นเมื่อเปรียบเทียบกับช่วงเวลาเดียวกันของปี 2568 จำนวน 3,306.15 kgCO2 หรือเพิ่มขึ้น เท่ากับ 23.98%</t>
   </si>
   <si>
     <r>
@@ -1174,46 +1090,7 @@
     <t xml:space="preserve">เดือนกันยายน 2569      </t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="20"/>
-        <color rgb="FF000000"/>
-        <rFont val="Cordia New"/>
-      </rPr>
-      <t xml:space="preserve">ปริมาณการปล่อยก๊าซเรือนกระจกในเดือนมีนาคม 2569 ลดลงเมื่อเปรียบเทียบกับช่วงเวลาเดียวกันของปี 2568 จำนวน </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="20"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Cordia New"/>
-      </rPr>
-      <t>463.37</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="20"/>
-        <color rgb="FF000000"/>
-        <rFont val="Cordia New"/>
-      </rPr>
-      <t xml:space="preserve"> kgCO2 หรือลดลง เท่ากับ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="20"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Cordia New"/>
-      </rPr>
-      <t>2.26</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="20"/>
-        <color rgb="FF000000"/>
-        <rFont val="Cordia New"/>
-      </rPr>
-      <t>%</t>
-    </r>
+    <t>ปริมาณการปล่อยก๊าซเรือนกระจกในเดือนมีนาคม 2569 ลดลงเมื่อเปรียบเทียบกับช่วงเวลาเดียวกันของปี 2568 จำนวน 2,181.62 kgCO2 หรือลดลง เท่ากับ 10.57%</t>
   </si>
   <si>
     <r>
@@ -1296,46 +1173,7 @@
     <t xml:space="preserve">เดือนตุลาคม 2569      </t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="20"/>
-        <color rgb="FF000000"/>
-        <rFont val="Cordia New"/>
-      </rPr>
-      <t xml:space="preserve">ปริมาณการปล่อยก๊าซเรือนกระจกในเดือนเมษายน 2569 เพิ่มขึ้นเมื่อเปรียบเทียบกับช่วงเวลาเดียวกันของปี 2568 จำนวน </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="20"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Cordia New"/>
-      </rPr>
-      <t>275.44</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="20"/>
-        <color rgb="FF000000"/>
-        <rFont val="Cordia New"/>
-      </rPr>
-      <t xml:space="preserve"> kgCO2 หรือเพิ่มขึ้น เท่ากับ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="20"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Cordia New"/>
-      </rPr>
-      <t>1.32</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="20"/>
-        <color rgb="FF000000"/>
-        <rFont val="Cordia New"/>
-      </rPr>
-      <t>%</t>
-    </r>
+    <t>ปริมาณการปล่อยก๊าซเรือนกระจกในเดือนเมษายน 2569 เพิ่มขึ้นเมื่อเปรียบเทียบกับช่วงเวลาเดียวกันของปี 2568 จำนวน 3,089.44 kgCO2 หรือเพิ่มขึ้น เท่ากับ 15.31%</t>
   </si>
   <si>
     <r>
@@ -1412,58 +1250,13 @@
     </r>
   </si>
   <si>
-    <t>ในเดือนเมษายน 2567 มีการใช้ห้องประชุมข้าวหอมมะลิสำหรับจัดประชุมที่มีผู้เข้าร่วมประชุมจำนวนมากหลายครั้ง ทำให้มีการใช้ทรัพยากรต่าง ๆ ของอาคารฯ เพิ่มมากขึ้น โดยเฉพาะไฟฟ้า</t>
-  </si>
-  <si>
-    <t>กำหนดมาตรการในการประหยัดพลังงานเพิ่มมากขึ้น โดยการประชาสัมพันธ์และติดป้ายรณรงค์ให้ผู้ที่เข้ามาใช้ห้องประชุมตระหนักถึงการใช้ทรัพยากรอย่างประหยัด</t>
-  </si>
-  <si>
     <t xml:space="preserve">เดือนพฤษภาคม 2569      </t>
   </si>
   <si>
     <t xml:space="preserve">เดือนพฤศจิกายน 2569      </t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="20"/>
-        <color rgb="FF000000"/>
-        <rFont val="Cordia New"/>
-      </rPr>
-      <t xml:space="preserve">ปริมาณการปล่อยก๊าซเรือนกระจกในเดือนพฤษภาคม 2569 ลดลงเมื่อเปรียบเทียบกับช่วงเวลาเดียวกันของปี 2568 จำนวน </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="20"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Cordia New"/>
-      </rPr>
-      <t>2,195.56</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="20"/>
-        <color rgb="FF000000"/>
-        <rFont val="Cordia New"/>
-      </rPr>
-      <t xml:space="preserve"> kgCO2 หรือลดลง เท่ากับ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="20"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Cordia New"/>
-      </rPr>
-      <t>9.50</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="20"/>
-        <color rgb="FF000000"/>
-        <rFont val="Cordia New"/>
-      </rPr>
-      <t>%</t>
-    </r>
+    <t>ปริมาณการปล่อยก๊าซเรือนกระจกในเดือนพฤษภาคม 2569 ลดลงเมื่อเปรียบเทียบกับช่วงเวลาเดียวกันของปี 2568 จำนวน 209.14 kgCO2 หรือลดลง เท่ากับ 0.95%</t>
   </si>
   <si>
     <r>
@@ -1546,46 +1339,7 @@
     <t xml:space="preserve">เดือนธันวาคม 2569      </t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="20"/>
-        <color rgb="FF000000"/>
-        <rFont val="Cordia New"/>
-      </rPr>
-      <t xml:space="preserve">ปริมาณการปล่อยก๊าซเรือนกระจกในเดือนมิถุนายน 2569 เพิ่มขึ้นเมื่อเปรียบเทียบกับช่วงเวลาเดียวกันของปี 2568 จำนวน </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="20"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Cordia New"/>
-      </rPr>
-      <t>2,453.80</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="20"/>
-        <color rgb="FF000000"/>
-        <rFont val="Cordia New"/>
-      </rPr>
-      <t xml:space="preserve"> kgCO2 หรือเพิ่มขึ้น เท่ากับ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="20"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Cordia New"/>
-      </rPr>
-      <t>10.54</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="20"/>
-        <color rgb="FF000000"/>
-        <rFont val="Cordia New"/>
-      </rPr>
-      <t>%</t>
-    </r>
+    <t>ปริมาณการปล่อยก๊าซเรือนกระจกในเดือนมิถุนายน 2569 เพิ่มขึ้นเมื่อเปรียบเทียบกับช่วงเวลาเดียวกันของปี 2568 จำนวน 3,387.24 kgCO2 หรือเพิ่มขึ้น เท่ากับ 16.09%</t>
   </si>
   <si>
     <r>
@@ -1660,6 +1414,12 @@
       </rPr>
       <t>%</t>
     </r>
+  </si>
+  <si>
+    <t>บุคลากรเกิดความตื่นตัวจากการเข้าร่วมโครงการสำนักงานสีเขียวเป็นปีแรก ประกอบกับมีการรณรงค์อย่างต่อเนื่อง ทำให้บุคลากรให้ความร่วมมือในการควบคุมการใช้พลังงาน ทรัพยากร และของเสีย อย่างพร้อมเพรียงกัน</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
   <si>
     <r>
@@ -2751,19 +2511,6 @@
       <name val="Cordia New"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color rgb="FFFF0000"/>
-      <name val="Cordia New"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color rgb="FFFF0000"/>
-      <name val="Cordia New"/>
-      <family val="2"/>
-      <charset val="222"/>
-    </font>
-    <font>
       <sz val="20"/>
       <color rgb="FF000000"/>
       <name val="Cordia New"/>
@@ -2793,6 +2540,19 @@
       <b/>
       <sz val="28"/>
       <name val="Cordia New"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Cordia New"/>
+      <family val="2"/>
+      <charset val="222"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Cordia New"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="20">
@@ -3698,27 +3458,83 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="46" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="48" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="46" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="46" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="47" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="41" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3747,98 +3563,14 @@
     <xf numFmtId="0" fontId="41" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3867,10 +3599,28 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3881,6 +3631,21 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="21" fillId="3" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="170" fontId="21" fillId="3" borderId="14" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="5" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="11" borderId="5" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3900,26 +3665,23 @@
     <xf numFmtId="0" fontId="20" fillId="10" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="21" fillId="3" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="2" fontId="52" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="21" fillId="3" borderId="14" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="2" fontId="53" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="5" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="2" fontId="53" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="2" fontId="53" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="2" fontId="53" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -4292,7 +4054,7 @@
                 <c:formatCode>#,##0.00</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>1.3533904980000002</c:v>
+                  <c:v>1.0862916220000003</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>132.27074056000001</c:v>
@@ -4301,7 +4063,7 @@
                   <c:v>11.445277089999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>145.06940814800001</c:v>
+                  <c:v>144.802309272</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4759,7 +4521,7 @@
                 <c:formatCode>#,##0.00</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>1.3533904980000002</c:v>
+                  <c:v>1.0862916220000003</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>132.27074056000001</c:v>
@@ -4768,7 +4530,7 @@
                   <c:v>11.445277089999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>145.06940814800001</c:v>
+                  <c:v>144.802309272</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5206,25 +4968,25 @@
                 <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"??_-;_-@_-</c:formatCode>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
-                  <c:v>16112.805033999999</c:v>
+                  <c:v>16128.563484</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>17194.532310000002</c:v>
+                  <c:v>17091.239096000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>18610.599704000004</c:v>
+                  <c:v>18458.331968000002</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>23402.449884000001</c:v>
+                  <c:v>23267.694582</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>21822.338800000001</c:v>
+                  <c:v>21731.597534</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>24335.76395</c:v>
+                  <c:v>24443.990244000001</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>23590.918465999999</c:v>
+                  <c:v>23680.892363999999</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0</c:v>
@@ -5242,10 +5004,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>145069.40814800002</c:v>
+                  <c:v>144802.30927199998</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>12089.117345666667</c:v>
+                  <c:v>12066.859105999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5805,25 +5567,25 @@
                       <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"??_-;_-@_-</c:formatCode>
                       <c:ptCount val="14"/>
                       <c:pt idx="0">
-                        <c:v>210.176614</c:v>
+                        <c:v>225.93506400000001</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>167.58769000000001</c:v>
+                        <c:v>64.294476000000003</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>259.64444400000002</c:v>
+                        <c:v>107.37670800000001</c:v>
                       </c:pt>
                       <c:pt idx="3">
-                        <c:v>241.830544</c:v>
+                        <c:v>107.075242</c:v>
                       </c:pt>
                       <c:pt idx="4">
-                        <c:v>224.72920000000002</c:v>
+                        <c:v>133.987934</c:v>
                       </c:pt>
                       <c:pt idx="5">
-                        <c:v>184.44238000000001</c:v>
+                        <c:v>292.66867400000001</c:v>
                       </c:pt>
                       <c:pt idx="6">
-                        <c:v>64.97962600000001</c:v>
+                        <c:v>154.95352400000002</c:v>
                       </c:pt>
                       <c:pt idx="7">
                         <c:v>0</c:v>
@@ -5841,10 +5603,10 @@
                         <c:v>0</c:v>
                       </c:pt>
                       <c:pt idx="12">
-                        <c:v>1353.3904980000002</c:v>
+                        <c:v>1086.2916220000002</c:v>
                       </c:pt>
                       <c:pt idx="13">
-                        <c:v>112.78254150000002</c:v>
+                        <c:v>90.524301833333354</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -8624,25 +8386,25 @@
                 <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"??_-;_-@_-</c:formatCode>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
-                  <c:v>169.60847404210526</c:v>
+                  <c:v>169.7743524631579</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>180.99507694736843</c:v>
+                  <c:v>179.90777995789475</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>195.90104951578951</c:v>
+                  <c:v>194.29823124210529</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>246.34157772631582</c:v>
+                  <c:v>244.92310086315788</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>229.70882947368423</c:v>
+                  <c:v>228.7536582526316</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>256.16593631578945</c:v>
+                  <c:v>257.3051604631579</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>248.32545753684209</c:v>
+                  <c:v>249.27255119999998</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0</c:v>
@@ -8660,10 +8422,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1527.0464015578948</c:v>
+                  <c:v>1524.2348344421052</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>127.25386679649124</c:v>
+                  <c:v>127.0195695368421</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9223,25 +8985,25 @@
                       <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"??_-;_-@_-</c:formatCode>
                       <c:ptCount val="14"/>
                       <c:pt idx="0">
-                        <c:v>210.176614</c:v>
+                        <c:v>225.93506400000001</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>167.58769000000001</c:v>
+                        <c:v>64.294476000000003</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>259.64444400000002</c:v>
+                        <c:v>107.37670800000001</c:v>
                       </c:pt>
                       <c:pt idx="3">
-                        <c:v>241.830544</c:v>
+                        <c:v>107.075242</c:v>
                       </c:pt>
                       <c:pt idx="4">
-                        <c:v>224.72920000000002</c:v>
+                        <c:v>133.987934</c:v>
                       </c:pt>
                       <c:pt idx="5">
-                        <c:v>184.44238000000001</c:v>
+                        <c:v>292.66867400000001</c:v>
                       </c:pt>
                       <c:pt idx="6">
-                        <c:v>64.97962600000001</c:v>
+                        <c:v>154.95352400000002</c:v>
                       </c:pt>
                       <c:pt idx="7">
                         <c:v>0</c:v>
@@ -9259,10 +9021,10 @@
                         <c:v>0</c:v>
                       </c:pt>
                       <c:pt idx="12">
-                        <c:v>1353.3904980000002</c:v>
+                        <c:v>1086.2916220000002</c:v>
                       </c:pt>
                       <c:pt idx="13">
-                        <c:v>112.78254150000002</c:v>
+                        <c:v>90.524301833333354</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -11671,25 +11433,25 @@
                       <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"??_-;_-@_-</c:formatCode>
                       <c:ptCount val="14"/>
                       <c:pt idx="0">
-                        <c:v>16112.805033999999</c:v>
+                        <c:v>16128.563484</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>17194.532310000002</c:v>
+                        <c:v>17091.239096000001</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>18610.599704000004</c:v>
+                        <c:v>18458.331968000002</c:v>
                       </c:pt>
                       <c:pt idx="3">
-                        <c:v>23402.449884000001</c:v>
+                        <c:v>23267.694582</c:v>
                       </c:pt>
                       <c:pt idx="4">
-                        <c:v>21822.338800000001</c:v>
+                        <c:v>21731.597534</c:v>
                       </c:pt>
                       <c:pt idx="5">
-                        <c:v>24335.76395</c:v>
+                        <c:v>24443.990244000001</c:v>
                       </c:pt>
                       <c:pt idx="6">
-                        <c:v>23590.918465999999</c:v>
+                        <c:v>23680.892363999999</c:v>
                       </c:pt>
                       <c:pt idx="7">
                         <c:v>0</c:v>
@@ -11707,10 +11469,10 @@
                         <c:v>0</c:v>
                       </c:pt>
                       <c:pt idx="12">
-                        <c:v>145069.40814800002</c:v>
+                        <c:v>144802.30927199998</c:v>
                       </c:pt>
                       <c:pt idx="13">
-                        <c:v>12089.117345666667</c:v>
+                        <c:v>12066.859105999998</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -11977,25 +11739,25 @@
                       <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"??_-;_-@_-</c:formatCode>
                       <c:ptCount val="14"/>
                       <c:pt idx="0">
-                        <c:v>5410.7520599999989</c:v>
+                        <c:v>5426.5105100000001</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>3409.4399600000015</c:v>
+                        <c:v>3306.1467460000003</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>-2029.3456200000001</c:v>
+                        <c:v>-2181.6133560000017</c:v>
                       </c:pt>
                       <c:pt idx="3">
-                        <c:v>3224.204020000001</c:v>
+                        <c:v>3089.4487179999996</c:v>
                       </c:pt>
                       <c:pt idx="4">
-                        <c:v>-118.39717999999993</c:v>
+                        <c:v>-209.13844600000084</c:v>
                       </c:pt>
                       <c:pt idx="5">
-                        <c:v>3279.0167099999999</c:v>
+                        <c:v>3387.2430039999999</c:v>
                       </c:pt>
                       <c:pt idx="6">
-                        <c:v>2383.1076199999952</c:v>
+                        <c:v>2473.0815179999954</c:v>
                       </c:pt>
                       <c:pt idx="7">
                         <c:v>-21501.694643999999</c:v>
@@ -12013,10 +11775,10 @@
                         <c:v>-13252.189980000001</c:v>
                       </c:pt>
                       <c:pt idx="12">
-                        <c:v>-77609.935563999985</c:v>
+                        <c:v>-77877.034440000018</c:v>
                       </c:pt>
                       <c:pt idx="13">
-                        <c:v>-6467.4946303333327</c:v>
+                        <c:v>-6489.7528700000021</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -12130,25 +11892,25 @@
                       <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"??_-;_-@_-</c:formatCode>
                       <c:ptCount val="14"/>
                       <c:pt idx="0">
-                        <c:v>50.558075849045956</c:v>
+                        <c:v>50.705322830894069</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>24.732804637322587</c:v>
+                        <c:v>23.98349363252543</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>-9.832126917702098</c:v>
+                        <c:v>-10.569860151050085</c:v>
                       </c:pt>
                       <c:pt idx="3">
-                        <c:v>15.978614007039642</c:v>
+                        <c:v>15.310789346223022</c:v>
                       </c:pt>
                       <c:pt idx="4">
-                        <c:v>-0.53962264578510244</c:v>
+                        <c:v>-0.95319704038479036</c:v>
                       </c:pt>
                       <c:pt idx="5">
-                        <c:v>15.572285085756672</c:v>
+                        <c:v>16.086259503393268</c:v>
                       </c:pt>
                       <c:pt idx="6">
-                        <c:v>11.236933586898113</c:v>
+                        <c:v>11.661182457530463</c:v>
                       </c:pt>
                       <c:pt idx="7">
                         <c:v>-100</c:v>
@@ -12166,10 +11928,10 @@
                         <c:v>-100</c:v>
                       </c:pt>
                       <c:pt idx="12">
-                        <c:v>-34.852777213308109</c:v>
+                        <c:v>-34.97272496937186</c:v>
                       </c:pt>
                       <c:pt idx="13">
-                        <c:v>-34.852777213308116</c:v>
+                        <c:v>-34.972724969371868</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -12898,7 +12660,7 @@
                 <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"??_-;_-@_-</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>145069.40814800002</c:v>
+                  <c:v>144802.30927199998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -18511,151 +18273,151 @@
       <c r="AE1" s="186"/>
     </row>
     <row r="2" spans="1:31" ht="45" customHeight="1">
-      <c r="A2" s="253" t="s">
+      <c r="A2" s="220" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="254"/>
-      <c r="C2" s="254"/>
-      <c r="D2" s="254"/>
-      <c r="E2" s="254"/>
-      <c r="F2" s="254"/>
-      <c r="G2" s="254"/>
-      <c r="H2" s="254"/>
-      <c r="I2" s="254"/>
-      <c r="J2" s="254"/>
-      <c r="K2" s="254"/>
-      <c r="L2" s="254"/>
-      <c r="M2" s="254"/>
-      <c r="N2" s="254"/>
-      <c r="O2" s="254"/>
-      <c r="P2" s="254"/>
-      <c r="Q2" s="254"/>
-      <c r="R2" s="254"/>
-      <c r="S2" s="254"/>
-      <c r="T2" s="254"/>
-      <c r="U2" s="254"/>
-      <c r="V2" s="254"/>
-      <c r="W2" s="254"/>
-      <c r="X2" s="254"/>
-      <c r="Y2" s="254"/>
-      <c r="Z2" s="254"/>
-      <c r="AA2" s="254"/>
-      <c r="AB2" s="254"/>
-      <c r="AC2" s="254"/>
-      <c r="AD2" s="254"/>
-      <c r="AE2" s="255"/>
+      <c r="B2" s="221"/>
+      <c r="C2" s="221"/>
+      <c r="D2" s="221"/>
+      <c r="E2" s="221"/>
+      <c r="F2" s="221"/>
+      <c r="G2" s="221"/>
+      <c r="H2" s="221"/>
+      <c r="I2" s="221"/>
+      <c r="J2" s="221"/>
+      <c r="K2" s="221"/>
+      <c r="L2" s="221"/>
+      <c r="M2" s="221"/>
+      <c r="N2" s="221"/>
+      <c r="O2" s="221"/>
+      <c r="P2" s="221"/>
+      <c r="Q2" s="221"/>
+      <c r="R2" s="221"/>
+      <c r="S2" s="221"/>
+      <c r="T2" s="221"/>
+      <c r="U2" s="221"/>
+      <c r="V2" s="221"/>
+      <c r="W2" s="221"/>
+      <c r="X2" s="221"/>
+      <c r="Y2" s="221"/>
+      <c r="Z2" s="221"/>
+      <c r="AA2" s="221"/>
+      <c r="AB2" s="221"/>
+      <c r="AC2" s="221"/>
+      <c r="AD2" s="221"/>
+      <c r="AE2" s="222"/>
     </row>
     <row r="3" spans="1:31" s="120" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A3" s="240" t="s">
+      <c r="A3" s="224" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="230" t="s">
+      <c r="B3" s="248" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="231"/>
-      <c r="D3" s="240" t="s">
+      <c r="C3" s="249"/>
+      <c r="D3" s="224" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="240" t="s">
+      <c r="E3" s="224" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="240" t="s">
+      <c r="F3" s="224" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="256" t="s">
+      <c r="G3" s="225" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="257"/>
-      <c r="I3" s="257"/>
-      <c r="J3" s="257"/>
-      <c r="K3" s="257"/>
-      <c r="L3" s="257"/>
-      <c r="M3" s="257"/>
-      <c r="N3" s="257"/>
-      <c r="O3" s="257"/>
-      <c r="P3" s="257"/>
-      <c r="Q3" s="257"/>
-      <c r="R3" s="257"/>
-      <c r="S3" s="257"/>
-      <c r="T3" s="257"/>
-      <c r="U3" s="257"/>
-      <c r="V3" s="257"/>
-      <c r="W3" s="257"/>
-      <c r="X3" s="257"/>
-      <c r="Y3" s="257"/>
-      <c r="Z3" s="257"/>
-      <c r="AA3" s="257"/>
-      <c r="AB3" s="257"/>
-      <c r="AC3" s="257"/>
-      <c r="AD3" s="257"/>
-      <c r="AE3" s="258"/>
+      <c r="H3" s="226"/>
+      <c r="I3" s="226"/>
+      <c r="J3" s="226"/>
+      <c r="K3" s="226"/>
+      <c r="L3" s="226"/>
+      <c r="M3" s="226"/>
+      <c r="N3" s="226"/>
+      <c r="O3" s="226"/>
+      <c r="P3" s="226"/>
+      <c r="Q3" s="226"/>
+      <c r="R3" s="226"/>
+      <c r="S3" s="226"/>
+      <c r="T3" s="226"/>
+      <c r="U3" s="226"/>
+      <c r="V3" s="226"/>
+      <c r="W3" s="226"/>
+      <c r="X3" s="226"/>
+      <c r="Y3" s="226"/>
+      <c r="Z3" s="226"/>
+      <c r="AA3" s="226"/>
+      <c r="AB3" s="226"/>
+      <c r="AC3" s="226"/>
+      <c r="AD3" s="226"/>
+      <c r="AE3" s="227"/>
     </row>
     <row r="4" spans="1:31" s="120" customFormat="1" ht="30" customHeight="1">
-      <c r="A4" s="240"/>
-      <c r="B4" s="232"/>
-      <c r="C4" s="233"/>
-      <c r="D4" s="240"/>
-      <c r="E4" s="240"/>
-      <c r="F4" s="240"/>
-      <c r="G4" s="241" t="s">
+      <c r="A4" s="224"/>
+      <c r="B4" s="250"/>
+      <c r="C4" s="251"/>
+      <c r="D4" s="224"/>
+      <c r="E4" s="224"/>
+      <c r="F4" s="224"/>
+      <c r="G4" s="223" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="241"/>
-      <c r="I4" s="241" t="s">
+      <c r="H4" s="223"/>
+      <c r="I4" s="223" t="s">
         <v>9</v>
       </c>
-      <c r="J4" s="241"/>
-      <c r="K4" s="241" t="s">
+      <c r="J4" s="223"/>
+      <c r="K4" s="223" t="s">
         <v>10</v>
       </c>
-      <c r="L4" s="241"/>
-      <c r="M4" s="241" t="s">
+      <c r="L4" s="223"/>
+      <c r="M4" s="223" t="s">
         <v>11</v>
       </c>
-      <c r="N4" s="241"/>
-      <c r="O4" s="241" t="s">
+      <c r="N4" s="223"/>
+      <c r="O4" s="223" t="s">
         <v>12</v>
       </c>
-      <c r="P4" s="241"/>
-      <c r="Q4" s="241" t="s">
+      <c r="P4" s="223"/>
+      <c r="Q4" s="223" t="s">
         <v>13</v>
       </c>
-      <c r="R4" s="241"/>
-      <c r="S4" s="241" t="s">
+      <c r="R4" s="223"/>
+      <c r="S4" s="223" t="s">
         <v>14</v>
       </c>
-      <c r="T4" s="241"/>
-      <c r="U4" s="241" t="s">
+      <c r="T4" s="223"/>
+      <c r="U4" s="223" t="s">
         <v>15</v>
       </c>
-      <c r="V4" s="241"/>
-      <c r="W4" s="241" t="s">
+      <c r="V4" s="223"/>
+      <c r="W4" s="223" t="s">
         <v>16</v>
       </c>
-      <c r="X4" s="241"/>
-      <c r="Y4" s="241" t="s">
+      <c r="X4" s="223"/>
+      <c r="Y4" s="223" t="s">
         <v>17</v>
       </c>
-      <c r="Z4" s="241"/>
-      <c r="AA4" s="241" t="s">
+      <c r="Z4" s="223"/>
+      <c r="AA4" s="223" t="s">
         <v>18</v>
       </c>
-      <c r="AB4" s="241"/>
-      <c r="AC4" s="241" t="s">
+      <c r="AB4" s="223"/>
+      <c r="AC4" s="223" t="s">
         <v>19</v>
       </c>
-      <c r="AD4" s="241"/>
-      <c r="AE4" s="259" t="s">
+      <c r="AD4" s="223"/>
+      <c r="AE4" s="228" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:31" s="120" customFormat="1" ht="30" customHeight="1">
-      <c r="A5" s="240"/>
-      <c r="B5" s="234"/>
-      <c r="C5" s="235"/>
-      <c r="D5" s="240"/>
-      <c r="E5" s="240"/>
-      <c r="F5" s="240"/>
+      <c r="A5" s="224"/>
+      <c r="B5" s="252"/>
+      <c r="C5" s="253"/>
+      <c r="D5" s="224"/>
+      <c r="E5" s="224"/>
+      <c r="F5" s="224"/>
       <c r="G5" s="189" t="s">
         <v>21</v>
       </c>
@@ -18728,16 +18490,16 @@
       <c r="AD5" s="189" t="s">
         <v>22</v>
       </c>
-      <c r="AE5" s="260"/>
+      <c r="AE5" s="229"/>
     </row>
     <row r="6" spans="1:31" ht="30" customHeight="1">
-      <c r="A6" s="240" t="s">
+      <c r="A6" s="224" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="236" t="s">
+      <c r="B6" s="237" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="237"/>
+      <c r="C6" s="238"/>
       <c r="D6" s="190"/>
       <c r="E6" s="190"/>
       <c r="F6" s="190"/>
@@ -18768,11 +18530,11 @@
       <c r="AE6" s="192"/>
     </row>
     <row r="7" spans="1:31" ht="30" customHeight="1">
-      <c r="A7" s="240"/>
-      <c r="B7" s="236" t="s">
+      <c r="A7" s="224"/>
+      <c r="B7" s="237" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="237"/>
+      <c r="C7" s="238"/>
       <c r="D7" s="190"/>
       <c r="E7" s="190"/>
       <c r="F7" s="190"/>
@@ -18803,11 +18565,11 @@
       <c r="AE7" s="192"/>
     </row>
     <row r="8" spans="1:31" ht="30" customHeight="1">
-      <c r="A8" s="240"/>
-      <c r="B8" s="238" t="s">
+      <c r="A8" s="224"/>
+      <c r="B8" s="239" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="239"/>
+      <c r="C8" s="240"/>
       <c r="D8" s="194">
         <v>2.7078000000000002</v>
       </c>
@@ -18897,11 +18659,11 @@
       </c>
     </row>
     <row r="9" spans="1:31" ht="30" customHeight="1">
-      <c r="A9" s="240"/>
-      <c r="B9" s="238" t="s">
+      <c r="A9" s="224"/>
+      <c r="B9" s="239" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="239"/>
+      <c r="C9" s="240"/>
       <c r="D9" s="194">
         <v>2.7078000000000002</v>
       </c>
@@ -18991,11 +18753,11 @@
       </c>
     </row>
     <row r="10" spans="1:31" ht="30" customHeight="1">
-      <c r="A10" s="240"/>
-      <c r="B10" s="236" t="s">
+      <c r="A10" s="224"/>
+      <c r="B10" s="237" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="237"/>
+      <c r="C10" s="238"/>
       <c r="D10" s="194"/>
       <c r="E10" s="190"/>
       <c r="F10" s="190"/>
@@ -19026,11 +18788,11 @@
       <c r="AE10" s="207"/>
     </row>
     <row r="11" spans="1:31" ht="30" customHeight="1">
-      <c r="A11" s="240"/>
-      <c r="B11" s="236" t="s">
+      <c r="A11" s="224"/>
+      <c r="B11" s="237" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="237"/>
+      <c r="C11" s="238"/>
       <c r="D11" s="194"/>
       <c r="E11" s="190"/>
       <c r="F11" s="190"/>
@@ -19061,11 +18823,11 @@
       <c r="AE11" s="207"/>
     </row>
     <row r="12" spans="1:31" ht="30" customHeight="1">
-      <c r="A12" s="240"/>
-      <c r="B12" s="238" t="s">
+      <c r="A12" s="224"/>
+      <c r="B12" s="239" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="239"/>
+      <c r="C12" s="240"/>
       <c r="D12" s="194">
         <v>2.7406000000000001</v>
       </c>
@@ -19075,54 +18837,54 @@
       <c r="F12" s="190" t="s">
         <v>28</v>
       </c>
-      <c r="G12" s="220">
-        <v>76.69</v>
+      <c r="G12" s="292">
+        <v>82.44</v>
       </c>
       <c r="H12" s="197">
         <f t="shared" ref="H12:H24" si="1">G12*D12</f>
-        <v>210.176614</v>
-      </c>
-      <c r="I12" s="221">
-        <v>61.15</v>
+        <v>225.93506400000001</v>
+      </c>
+      <c r="I12" s="291">
+        <v>23.46</v>
       </c>
       <c r="J12" s="197">
         <f t="shared" ref="J12:J24" si="2">I12*D12</f>
-        <v>167.58769000000001</v>
-      </c>
-      <c r="K12" s="222">
-        <v>94.74</v>
+        <v>64.294476000000003</v>
+      </c>
+      <c r="K12" s="290">
+        <v>39.18</v>
       </c>
       <c r="L12" s="197">
         <f t="shared" ref="L12:L24" si="3">K12*D12</f>
-        <v>259.64444400000002</v>
-      </c>
-      <c r="M12" s="223">
-        <v>88.24</v>
+        <v>107.37670800000001</v>
+      </c>
+      <c r="M12" s="289">
+        <v>39.07</v>
       </c>
       <c r="N12" s="197">
         <f t="shared" ref="N12:N24" si="4">M12*D12</f>
-        <v>241.830544</v>
-      </c>
-      <c r="O12" s="223">
-        <v>82</v>
+        <v>107.075242</v>
+      </c>
+      <c r="O12" s="289">
+        <v>48.89</v>
       </c>
       <c r="P12" s="197">
         <f t="shared" ref="P12:P24" si="5">O12*D12</f>
-        <v>224.72920000000002</v>
-      </c>
-      <c r="Q12" s="224">
-        <v>67.3</v>
+        <v>133.987934</v>
+      </c>
+      <c r="Q12" s="288">
+        <v>106.79</v>
       </c>
       <c r="R12" s="197">
         <f t="shared" ref="R12:R24" si="6">Q12*D12</f>
-        <v>184.44238000000001</v>
-      </c>
-      <c r="S12" s="224">
-        <v>23.71</v>
+        <v>292.66867400000001</v>
+      </c>
+      <c r="S12" s="288">
+        <v>56.54</v>
       </c>
       <c r="T12" s="197">
         <f t="shared" ref="T12:T24" si="7">S12*D12</f>
-        <v>64.97962600000001</v>
+        <v>154.95352400000002</v>
       </c>
       <c r="U12" s="196"/>
       <c r="V12" s="197">
@@ -19151,15 +18913,15 @@
       </c>
       <c r="AE12" s="207">
         <f t="shared" si="0"/>
-        <v>1353.3904980000002</v>
+        <v>1086.2916220000002</v>
       </c>
     </row>
     <row r="13" spans="1:31" ht="30" customHeight="1">
-      <c r="A13" s="240"/>
-      <c r="B13" s="238" t="s">
+      <c r="A13" s="224"/>
+      <c r="B13" s="239" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="239"/>
+      <c r="C13" s="240"/>
       <c r="D13" s="194">
         <v>2.2393999999999998</v>
       </c>
@@ -19249,11 +19011,11 @@
       </c>
     </row>
     <row r="14" spans="1:31" ht="30" customHeight="1">
-      <c r="A14" s="240"/>
-      <c r="B14" s="238" t="s">
+      <c r="A14" s="224"/>
+      <c r="B14" s="239" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="239"/>
+      <c r="C14" s="240"/>
       <c r="D14" s="194">
         <v>2.2393999999999998</v>
       </c>
@@ -19343,11 +19105,11 @@
       </c>
     </row>
     <row r="15" spans="1:31" ht="30" customHeight="1">
-      <c r="A15" s="240"/>
-      <c r="B15" s="236" t="s">
+      <c r="A15" s="224"/>
+      <c r="B15" s="237" t="s">
         <v>35</v>
       </c>
-      <c r="C15" s="237"/>
+      <c r="C15" s="238"/>
       <c r="D15" s="194">
         <v>1</v>
       </c>
@@ -19437,11 +19199,11 @@
       </c>
     </row>
     <row r="16" spans="1:31" ht="30" customHeight="1">
-      <c r="A16" s="240"/>
-      <c r="B16" s="245" t="s">
+      <c r="A16" s="224"/>
+      <c r="B16" s="233" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="246"/>
+      <c r="C16" s="234"/>
       <c r="D16" s="198">
         <v>28</v>
       </c>
@@ -19538,11 +19300,11 @@
       </c>
     </row>
     <row r="17" spans="1:47" ht="30" customHeight="1">
-      <c r="A17" s="240"/>
-      <c r="B17" s="247" t="s">
+      <c r="A17" s="224"/>
+      <c r="B17" s="235" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="248"/>
+      <c r="C17" s="236"/>
       <c r="D17" s="194">
         <v>28</v>
       </c>
@@ -19639,11 +19401,11 @@
       </c>
     </row>
     <row r="18" spans="1:47" ht="30" customHeight="1">
-      <c r="A18" s="240"/>
-      <c r="B18" s="236" t="s">
+      <c r="A18" s="224"/>
+      <c r="B18" s="237" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="237"/>
+      <c r="C18" s="238"/>
       <c r="D18" s="194">
         <v>1760</v>
       </c>
@@ -19680,11 +19442,11 @@
       <c r="AE18" s="207"/>
     </row>
     <row r="19" spans="1:47" ht="30" customHeight="1">
-      <c r="A19" s="240"/>
-      <c r="B19" s="236" t="s">
+      <c r="A19" s="224"/>
+      <c r="B19" s="237" t="s">
         <v>45</v>
       </c>
-      <c r="C19" s="237"/>
+      <c r="C19" s="238"/>
       <c r="D19" s="194">
         <v>677</v>
       </c>
@@ -19777,10 +19539,10 @@
       <c r="A20" s="189" t="s">
         <v>48</v>
       </c>
-      <c r="B20" s="238" t="s">
+      <c r="B20" s="239" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="239"/>
+      <c r="C20" s="240"/>
       <c r="D20" s="194">
         <v>0.49990000000000001</v>
       </c>
@@ -19870,13 +19632,13 @@
       </c>
     </row>
     <row r="21" spans="1:47" ht="30" customHeight="1">
-      <c r="A21" s="240" t="s">
+      <c r="A21" s="224" t="s">
         <v>52</v>
       </c>
-      <c r="B21" s="238" t="s">
+      <c r="B21" s="239" t="s">
         <v>53</v>
       </c>
-      <c r="C21" s="239"/>
+      <c r="C21" s="240"/>
       <c r="D21" s="194">
         <v>2.1019999999999999</v>
       </c>
@@ -19966,11 +19728,11 @@
       </c>
     </row>
     <row r="22" spans="1:47" ht="30" customHeight="1">
-      <c r="A22" s="240"/>
-      <c r="B22" s="238" t="s">
+      <c r="A22" s="224"/>
+      <c r="B22" s="239" t="s">
         <v>55</v>
       </c>
-      <c r="C22" s="239"/>
+      <c r="C22" s="240"/>
       <c r="D22" s="194">
         <v>0.79479999999999995</v>
       </c>
@@ -20060,11 +19822,11 @@
       </c>
     </row>
     <row r="23" spans="1:47" ht="30" customHeight="1">
-      <c r="A23" s="240"/>
-      <c r="B23" s="238" t="s">
+      <c r="A23" s="224"/>
+      <c r="B23" s="239" t="s">
         <v>58</v>
       </c>
-      <c r="C23" s="239"/>
+      <c r="C23" s="240"/>
       <c r="D23" s="194">
         <v>0.54100000000000004</v>
       </c>
@@ -20154,11 +19916,11 @@
       </c>
     </row>
     <row r="24" spans="1:47" ht="30" customHeight="1">
-      <c r="A24" s="240"/>
-      <c r="B24" s="249" t="s">
+      <c r="A24" s="224"/>
+      <c r="B24" s="241" t="s">
         <v>59</v>
       </c>
-      <c r="C24" s="250"/>
+      <c r="C24" s="242"/>
       <c r="D24" s="194">
         <v>2.3199999999999998</v>
       </c>
@@ -20248,11 +20010,11 @@
       </c>
     </row>
     <row r="25" spans="1:47" ht="30" customHeight="1">
-      <c r="A25" s="240"/>
-      <c r="B25" s="251" t="s">
+      <c r="A25" s="224"/>
+      <c r="B25" s="243" t="s">
         <v>60</v>
       </c>
-      <c r="C25" s="252"/>
+      <c r="C25" s="244"/>
       <c r="D25" s="194">
         <v>2.7078000000000002</v>
       </c>
@@ -20356,48 +20118,48 @@
       <c r="AU25" s="121"/>
     </row>
     <row r="26" spans="1:47" ht="30" customHeight="1">
-      <c r="A26" s="244" t="s">
+      <c r="A26" s="232" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="244"/>
-      <c r="C26" s="244"/>
-      <c r="D26" s="244"/>
-      <c r="E26" s="244"/>
-      <c r="F26" s="244"/>
+      <c r="B26" s="232"/>
+      <c r="C26" s="232"/>
+      <c r="D26" s="232"/>
+      <c r="E26" s="232"/>
+      <c r="F26" s="232"/>
       <c r="G26" s="191"/>
       <c r="H26" s="197">
         <f>SUM(H6:H25)</f>
-        <v>16112.805033999999</v>
+        <v>16128.563484</v>
       </c>
       <c r="I26" s="197"/>
       <c r="J26" s="197">
         <f t="shared" ref="J26:AE26" si="26">SUM(J6:J25)</f>
-        <v>17194.532310000002</v>
+        <v>17091.239096000001</v>
       </c>
       <c r="K26" s="197"/>
       <c r="L26" s="197">
         <f t="shared" si="26"/>
-        <v>18610.599704000004</v>
+        <v>18458.331968000002</v>
       </c>
       <c r="M26" s="197"/>
       <c r="N26" s="197">
         <f t="shared" si="26"/>
-        <v>23402.449884000001</v>
+        <v>23267.694582</v>
       </c>
       <c r="O26" s="197"/>
       <c r="P26" s="197">
         <f t="shared" si="26"/>
-        <v>21822.338800000001</v>
+        <v>21731.597534</v>
       </c>
       <c r="Q26" s="196"/>
       <c r="R26" s="197">
         <f t="shared" si="26"/>
-        <v>24335.76395</v>
+        <v>24443.990244000001</v>
       </c>
       <c r="S26" s="196"/>
       <c r="T26" s="197">
         <f t="shared" si="26"/>
-        <v>23590.918465999999</v>
+        <v>23680.892363999999</v>
       </c>
       <c r="U26" s="196"/>
       <c r="V26" s="197">
@@ -20426,7 +20188,7 @@
       </c>
       <c r="AE26" s="197">
         <f t="shared" si="26"/>
-        <v>145069.40814799999</v>
+        <v>144802.30927199998</v>
       </c>
       <c r="AG26" s="121"/>
       <c r="AH26" s="121"/>
@@ -20718,14 +20480,14 @@
       <c r="C37" s="204" t="s">
         <v>70</v>
       </c>
-      <c r="D37" s="242" t="s">
+      <c r="D37" s="230" t="s">
         <v>71</v>
       </c>
-      <c r="E37" s="242"/>
-      <c r="F37" s="243" t="s">
+      <c r="E37" s="230"/>
+      <c r="F37" s="231" t="s">
         <v>72</v>
       </c>
-      <c r="G37" s="243"/>
+      <c r="G37" s="231"/>
       <c r="K37" s="121"/>
       <c r="AG37" s="121"/>
       <c r="AH37" s="121"/>
@@ -20783,7 +20545,7 @@
       </c>
       <c r="E39" s="212">
         <f>(SUM(AE8:AE19))/1000</f>
-        <v>1.3533904980000002</v>
+        <v>1.0862916220000003</v>
       </c>
       <c r="F39" s="214">
         <f>D39*100/$D$42</f>
@@ -20791,7 +20553,7 @@
       </c>
       <c r="G39" s="213">
         <f>(E39*100)/$E$42</f>
-        <v>0.93292618704232211</v>
+        <v>0.75018943237948299</v>
       </c>
       <c r="K39" s="121"/>
       <c r="AG39" s="121"/>
@@ -20826,7 +20588,7 @@
       </c>
       <c r="G40" s="213">
         <f>(E40*100)/$E$42</f>
-        <v>91.177555798019952</v>
+        <v>91.345739736470364</v>
       </c>
       <c r="K40" s="121"/>
       <c r="AG40" s="121"/>
@@ -20861,7 +20623,7 @@
       </c>
       <c r="G41" s="213">
         <f>(E41*100)/$E$42</f>
-        <v>7.8895180149377273</v>
+        <v>7.9040708311501628</v>
       </c>
       <c r="K41" s="121"/>
       <c r="AG41" s="121"/>
@@ -20890,7 +20652,7 @@
       </c>
       <c r="E42" s="119">
         <f>SUM(E39:E41)</f>
-        <v>145.06940814800001</v>
+        <v>144.802309272</v>
       </c>
       <c r="F42" s="201">
         <f t="shared" si="27"/>
@@ -20986,43 +20748,43 @@
       <c r="AS48" s="126"/>
     </row>
     <row r="49" spans="1:47" ht="30" customHeight="1">
-      <c r="C49" s="227" t="s">
+      <c r="C49" s="245" t="s">
         <v>79</v>
       </c>
-      <c r="D49" s="227"/>
-      <c r="E49" s="227"/>
-      <c r="F49" s="227"/>
-      <c r="G49" s="227"/>
-      <c r="H49" s="227"/>
-      <c r="I49" s="227"/>
-      <c r="J49" s="227"/>
-      <c r="K49" s="227"/>
-      <c r="L49" s="227"/>
-      <c r="M49" s="227"/>
-      <c r="N49" s="227"/>
-      <c r="O49" s="227"/>
-      <c r="P49" s="227"/>
-      <c r="Q49" s="227"/>
+      <c r="D49" s="245"/>
+      <c r="E49" s="245"/>
+      <c r="F49" s="245"/>
+      <c r="G49" s="245"/>
+      <c r="H49" s="245"/>
+      <c r="I49" s="245"/>
+      <c r="J49" s="245"/>
+      <c r="K49" s="245"/>
+      <c r="L49" s="245"/>
+      <c r="M49" s="245"/>
+      <c r="N49" s="245"/>
+      <c r="O49" s="245"/>
+      <c r="P49" s="245"/>
+      <c r="Q49" s="245"/>
       <c r="AS49" s="126"/>
     </row>
     <row r="50" spans="1:47" ht="30" customHeight="1">
       <c r="A50" s="170"/>
       <c r="B50" s="138"/>
-      <c r="C50" s="228"/>
-      <c r="D50" s="228"/>
-      <c r="E50" s="228"/>
-      <c r="F50" s="228"/>
-      <c r="G50" s="228"/>
-      <c r="H50" s="228"/>
-      <c r="I50" s="228"/>
-      <c r="J50" s="228"/>
-      <c r="K50" s="228"/>
-      <c r="L50" s="228"/>
-      <c r="M50" s="228"/>
-      <c r="N50" s="228"/>
-      <c r="O50" s="228"/>
-      <c r="P50" s="228"/>
-      <c r="Q50" s="228"/>
+      <c r="C50" s="246"/>
+      <c r="D50" s="246"/>
+      <c r="E50" s="246"/>
+      <c r="F50" s="246"/>
+      <c r="G50" s="246"/>
+      <c r="H50" s="246"/>
+      <c r="I50" s="246"/>
+      <c r="J50" s="246"/>
+      <c r="K50" s="246"/>
+      <c r="L50" s="246"/>
+      <c r="M50" s="246"/>
+      <c r="N50" s="246"/>
+      <c r="O50" s="246"/>
+      <c r="P50" s="246"/>
+      <c r="Q50" s="246"/>
       <c r="AG50" s="121"/>
       <c r="AH50" s="121"/>
       <c r="AI50" s="121"/>
@@ -21269,31 +21031,31 @@
       </c>
       <c r="D54" s="143">
         <f>H12</f>
-        <v>210.176614</v>
+        <v>225.93506400000001</v>
       </c>
       <c r="E54" s="143">
         <f t="shared" ref="E54:E67" si="30">J12</f>
-        <v>167.58769000000001</v>
+        <v>64.294476000000003</v>
       </c>
       <c r="F54" s="143">
         <f t="shared" ref="F54:F67" si="31">L12</f>
-        <v>259.64444400000002</v>
+        <v>107.37670800000001</v>
       </c>
       <c r="G54" s="143">
         <f t="shared" ref="G54:G67" si="32">N12</f>
-        <v>241.830544</v>
+        <v>107.075242</v>
       </c>
       <c r="H54" s="143">
         <f t="shared" ref="H54:H67" si="33">P12</f>
-        <v>224.72920000000002</v>
+        <v>133.987934</v>
       </c>
       <c r="I54" s="143">
         <f t="shared" ref="I54:I67" si="34">R12</f>
-        <v>184.44238000000001</v>
+        <v>292.66867400000001</v>
       </c>
       <c r="J54" s="143">
         <f t="shared" ref="J54:J67" si="35">T12</f>
-        <v>64.97962600000001</v>
+        <v>154.95352400000002</v>
       </c>
       <c r="K54" s="143">
         <f t="shared" ref="K54:K67" si="36">V12</f>
@@ -21317,11 +21079,11 @@
       </c>
       <c r="P54" s="143">
         <f t="shared" si="28"/>
-        <v>1353.3904980000002</v>
+        <v>1086.2916220000002</v>
       </c>
       <c r="Q54" s="143">
         <f t="shared" si="29"/>
-        <v>112.78254150000002</v>
+        <v>90.524301833333354</v>
       </c>
       <c r="AG54" s="121"/>
       <c r="AH54" s="121"/>
@@ -22471,31 +22233,31 @@
       </c>
       <c r="D70" s="215">
         <f>SUM(D52:D67)</f>
-        <v>16112.805033999999</v>
+        <v>16128.563484</v>
       </c>
       <c r="E70" s="215">
         <f t="shared" ref="E70:H70" si="42">SUM(E52:E67)</f>
-        <v>17194.532310000002</v>
+        <v>17091.239096000001</v>
       </c>
       <c r="F70" s="215">
         <f t="shared" si="42"/>
-        <v>18610.599704000004</v>
+        <v>18458.331968000002</v>
       </c>
       <c r="G70" s="215">
         <f t="shared" si="42"/>
-        <v>23402.449884000001</v>
+        <v>23267.694582</v>
       </c>
       <c r="H70" s="215">
         <f t="shared" si="42"/>
-        <v>21822.338800000001</v>
+        <v>21731.597534</v>
       </c>
       <c r="I70" s="215">
         <f t="shared" ref="I70:O70" si="43">SUM(I52:I67)</f>
-        <v>24335.76395</v>
+        <v>24443.990244000001</v>
       </c>
       <c r="J70" s="215">
         <f t="shared" si="43"/>
-        <v>23590.918465999999</v>
+        <v>23680.892363999999</v>
       </c>
       <c r="K70" s="215">
         <f t="shared" si="43"/>
@@ -22519,11 +22281,11 @@
       </c>
       <c r="P70" s="143">
         <f t="shared" si="28"/>
-        <v>145069.40814800002</v>
+        <v>144802.30927199998</v>
       </c>
       <c r="Q70" s="143">
         <f t="shared" si="29"/>
-        <v>12089.117345666667</v>
+        <v>12066.859105999998</v>
       </c>
       <c r="AG70" s="121"/>
       <c r="AH70" s="121"/>
@@ -22621,31 +22383,31 @@
       </c>
       <c r="D72" s="143">
         <f>D70-D71</f>
-        <v>5410.7520599999989</v>
+        <v>5426.5105100000001</v>
       </c>
       <c r="E72" s="143">
         <f t="shared" ref="E72:H72" si="44">E70-E71</f>
-        <v>3409.4399600000015</v>
+        <v>3306.1467460000003</v>
       </c>
       <c r="F72" s="143">
         <f t="shared" si="44"/>
-        <v>-2029.3456200000001</v>
+        <v>-2181.6133560000017</v>
       </c>
       <c r="G72" s="143">
         <f t="shared" si="44"/>
-        <v>3224.204020000001</v>
+        <v>3089.4487179999996</v>
       </c>
       <c r="H72" s="143">
         <f t="shared" si="44"/>
-        <v>-118.39717999999993</v>
+        <v>-209.13844600000084</v>
       </c>
       <c r="I72" s="143">
         <f t="shared" ref="I72:O72" si="45">I70-I71</f>
-        <v>3279.0167099999999</v>
+        <v>3387.2430039999999</v>
       </c>
       <c r="J72" s="143">
         <f t="shared" si="45"/>
-        <v>2383.1076199999952</v>
+        <v>2473.0815179999954</v>
       </c>
       <c r="K72" s="143">
         <f t="shared" si="45"/>
@@ -22669,11 +22431,11 @@
       </c>
       <c r="P72" s="143">
         <f t="shared" ref="P72" si="46">P70-P71</f>
-        <v>-77609.935563999985</v>
+        <v>-77877.034440000018</v>
       </c>
       <c r="Q72" s="143">
         <f t="shared" ref="Q72" si="47">Q70-Q71</f>
-        <v>-6467.4946303333327</v>
+        <v>-6489.7528700000021</v>
       </c>
       <c r="AG72" s="121"/>
       <c r="AH72" s="121"/>
@@ -22696,31 +22458,31 @@
       </c>
       <c r="D73" s="149">
         <f>D72*100/D71</f>
-        <v>50.558075849045956</v>
+        <v>50.705322830894069</v>
       </c>
       <c r="E73" s="149">
         <f t="shared" ref="E73:H73" si="48">E72*100/E71</f>
-        <v>24.732804637322587</v>
+        <v>23.98349363252543</v>
       </c>
       <c r="F73" s="149">
         <f t="shared" si="48"/>
-        <v>-9.832126917702098</v>
+        <v>-10.569860151050085</v>
       </c>
       <c r="G73" s="149">
         <f t="shared" si="48"/>
-        <v>15.978614007039642</v>
+        <v>15.310789346223022</v>
       </c>
       <c r="H73" s="149">
         <f t="shared" si="48"/>
-        <v>-0.53962264578510244</v>
+        <v>-0.95319704038479036</v>
       </c>
       <c r="I73" s="149">
         <f t="shared" ref="I73:Q73" si="49">I72*100/I71</f>
-        <v>15.572285085756672</v>
+        <v>16.086259503393268</v>
       </c>
       <c r="J73" s="149">
         <f t="shared" si="49"/>
-        <v>11.236933586898113</v>
+        <v>11.661182457530463</v>
       </c>
       <c r="K73" s="149">
         <f t="shared" si="49"/>
@@ -22744,11 +22506,11 @@
       </c>
       <c r="P73" s="149">
         <f t="shared" si="49"/>
-        <v>-34.852777213308109</v>
+        <v>-34.97272496937186</v>
       </c>
       <c r="Q73" s="149">
         <f t="shared" si="49"/>
-        <v>-34.852777213308116</v>
+        <v>-34.972724969371868</v>
       </c>
     </row>
     <row r="74" spans="1:47" ht="30" customHeight="1">
@@ -22757,31 +22519,31 @@
       </c>
       <c r="D74" s="215">
         <f>D70/D68</f>
-        <v>169.60847404210526</v>
+        <v>169.7743524631579</v>
       </c>
       <c r="E74" s="215">
         <f t="shared" ref="E74:O74" si="50">E70/E68</f>
-        <v>180.99507694736843</v>
+        <v>179.90777995789475</v>
       </c>
       <c r="F74" s="215">
         <f t="shared" si="50"/>
-        <v>195.90104951578951</v>
+        <v>194.29823124210529</v>
       </c>
       <c r="G74" s="215">
         <f t="shared" si="50"/>
-        <v>246.34157772631582</v>
+        <v>244.92310086315788</v>
       </c>
       <c r="H74" s="215">
         <f t="shared" si="50"/>
-        <v>229.70882947368423</v>
+        <v>228.7536582526316</v>
       </c>
       <c r="I74" s="215">
         <f t="shared" si="50"/>
-        <v>256.16593631578945</v>
+        <v>257.3051604631579</v>
       </c>
       <c r="J74" s="215">
         <f t="shared" si="50"/>
-        <v>248.32545753684209</v>
+        <v>249.27255119999998</v>
       </c>
       <c r="K74" s="215">
         <f t="shared" si="50"/>
@@ -22805,11 +22567,11 @@
       </c>
       <c r="P74" s="143">
         <f>SUM(D74:O74)</f>
-        <v>1527.0464015578948</v>
+        <v>1524.2348344421052</v>
       </c>
       <c r="Q74" s="143">
         <f>AVERAGE(D74:O74)</f>
-        <v>127.25386679649124</v>
+        <v>127.0195695368421</v>
       </c>
     </row>
     <row r="75" spans="1:47" ht="30" customHeight="1">
@@ -22879,31 +22641,31 @@
       </c>
       <c r="D76" s="143">
         <f>D74-D75</f>
-        <v>56.955284842105257</v>
+        <v>57.121163263157896</v>
       </c>
       <c r="E76" s="143">
         <f t="shared" ref="E76:H76" si="52">E74-E75</f>
-        <v>35.888841684210519</v>
+        <v>34.801544694736833</v>
       </c>
       <c r="F76" s="143">
         <f t="shared" si="52"/>
-        <v>-21.361532842105277</v>
+        <v>-22.964351115789498</v>
       </c>
       <c r="G76" s="143">
         <f t="shared" si="52"/>
-        <v>33.938989684210554</v>
+        <v>32.52051282105262</v>
       </c>
       <c r="H76" s="143">
         <f t="shared" si="52"/>
-        <v>-1.2462861052631524</v>
+        <v>-2.2014573263157899</v>
       </c>
       <c r="I76" s="143">
         <f t="shared" ref="I76:P76" si="53">I74-I75</f>
-        <v>34.515965368421035</v>
+        <v>35.655189515789488</v>
       </c>
       <c r="J76" s="143">
         <f t="shared" si="53"/>
-        <v>25.085343368421007</v>
+        <v>26.032437031578894</v>
       </c>
       <c r="K76" s="143">
         <f t="shared" si="53"/>
@@ -22927,11 +22689,11 @@
       </c>
       <c r="P76" s="143">
         <f t="shared" si="53"/>
-        <v>-816.9466901473686</v>
+        <v>-819.75825726315816</v>
       </c>
       <c r="Q76" s="143">
         <f t="shared" ref="Q76" si="54">Q74-Q75</f>
-        <v>-68.078890845614055</v>
+        <v>-68.313188105263194</v>
       </c>
       <c r="R76" s="120"/>
       <c r="S76" s="120"/>
@@ -22949,31 +22711,31 @@
       </c>
       <c r="D77" s="143">
         <f>D76*100/D75</f>
-        <v>50.558075849045963</v>
+        <v>50.705322830894076</v>
       </c>
       <c r="E77" s="143">
         <f t="shared" ref="E77:H77" si="55">E76*100/E75</f>
-        <v>24.73280463732257</v>
+        <v>23.98349363252542</v>
       </c>
       <c r="F77" s="143">
         <f t="shared" si="55"/>
-        <v>-9.8321269177021033</v>
+        <v>-10.569860151050086</v>
       </c>
       <c r="G77" s="143">
         <f t="shared" si="55"/>
-        <v>15.978614007039649</v>
+        <v>15.31078934622302</v>
       </c>
       <c r="H77" s="143">
         <f t="shared" si="55"/>
-        <v>-0.53962264578510033</v>
+        <v>-0.9531970403847867</v>
       </c>
       <c r="I77" s="143">
         <f t="shared" ref="I77:Q77" si="56">I76*100/I75</f>
-        <v>15.572285085756665</v>
+        <v>16.086259503393276</v>
       </c>
       <c r="J77" s="143">
         <f t="shared" si="56"/>
-        <v>11.236933586898116</v>
+        <v>11.661182457530462</v>
       </c>
       <c r="K77" s="143">
         <f t="shared" si="56"/>
@@ -22997,11 +22759,11 @@
       </c>
       <c r="P77" s="143">
         <f t="shared" si="56"/>
-        <v>-34.852777213308123</v>
+        <v>-34.97272496937186</v>
       </c>
       <c r="Q77" s="143">
         <f t="shared" si="56"/>
-        <v>-34.852777213308123</v>
+        <v>-34.972724969371868</v>
       </c>
     </row>
     <row r="78" spans="1:47" ht="30" customHeight="1">
@@ -23462,39 +23224,39 @@
       <c r="AU94" s="121"/>
     </row>
     <row r="95" spans="1:47" s="151" customFormat="1" ht="30" customHeight="1">
-      <c r="A95" s="229" t="s">
+      <c r="A95" s="247" t="s">
         <v>103</v>
       </c>
-      <c r="B95" s="229"/>
-      <c r="C95" s="229"/>
-      <c r="D95" s="229"/>
-      <c r="E95" s="229"/>
-      <c r="F95" s="229"/>
-      <c r="G95" s="229"/>
-      <c r="H95" s="229"/>
-      <c r="I95" s="229"/>
-      <c r="J95" s="229"/>
-      <c r="K95" s="229"/>
-      <c r="L95" s="229"/>
-      <c r="M95" s="229"/>
-      <c r="N95" s="229"/>
-      <c r="O95" s="229"/>
-      <c r="P95" s="229"/>
-      <c r="Q95" s="229"/>
-      <c r="R95" s="229"/>
-      <c r="S95" s="229"/>
-      <c r="T95" s="229"/>
-      <c r="U95" s="229"/>
-      <c r="V95" s="229"/>
-      <c r="W95" s="229"/>
-      <c r="X95" s="229"/>
-      <c r="Y95" s="229"/>
-      <c r="Z95" s="229"/>
-      <c r="AA95" s="229"/>
-      <c r="AB95" s="229"/>
-      <c r="AC95" s="229"/>
-      <c r="AD95" s="229"/>
-      <c r="AE95" s="229"/>
+      <c r="B95" s="247"/>
+      <c r="C95" s="247"/>
+      <c r="D95" s="247"/>
+      <c r="E95" s="247"/>
+      <c r="F95" s="247"/>
+      <c r="G95" s="247"/>
+      <c r="H95" s="247"/>
+      <c r="I95" s="247"/>
+      <c r="J95" s="247"/>
+      <c r="K95" s="247"/>
+      <c r="L95" s="247"/>
+      <c r="M95" s="247"/>
+      <c r="N95" s="247"/>
+      <c r="O95" s="247"/>
+      <c r="P95" s="247"/>
+      <c r="Q95" s="247"/>
+      <c r="R95" s="247"/>
+      <c r="S95" s="247"/>
+      <c r="T95" s="247"/>
+      <c r="U95" s="247"/>
+      <c r="V95" s="247"/>
+      <c r="W95" s="247"/>
+      <c r="X95" s="247"/>
+      <c r="Y95" s="247"/>
+      <c r="Z95" s="247"/>
+      <c r="AA95" s="247"/>
+      <c r="AB95" s="247"/>
+      <c r="AC95" s="247"/>
+      <c r="AD95" s="247"/>
+      <c r="AE95" s="247"/>
       <c r="AF95" s="150"/>
       <c r="AG95" s="150"/>
       <c r="AH95" s="150"/>
@@ -23504,37 +23266,37 @@
       <c r="AL95" s="150"/>
     </row>
     <row r="96" spans="1:47" s="151" customFormat="1" ht="30" customHeight="1">
-      <c r="A96" s="229"/>
-      <c r="B96" s="229"/>
-      <c r="C96" s="229"/>
-      <c r="D96" s="229"/>
-      <c r="E96" s="229"/>
-      <c r="F96" s="229"/>
-      <c r="G96" s="229"/>
-      <c r="H96" s="229"/>
-      <c r="I96" s="229"/>
-      <c r="J96" s="229"/>
-      <c r="K96" s="229"/>
-      <c r="L96" s="229"/>
-      <c r="M96" s="229"/>
-      <c r="N96" s="229"/>
-      <c r="O96" s="229"/>
-      <c r="P96" s="229"/>
-      <c r="Q96" s="229"/>
-      <c r="R96" s="229"/>
-      <c r="S96" s="229"/>
-      <c r="T96" s="229"/>
-      <c r="U96" s="229"/>
-      <c r="V96" s="229"/>
-      <c r="W96" s="229"/>
-      <c r="X96" s="229"/>
-      <c r="Y96" s="229"/>
-      <c r="Z96" s="229"/>
-      <c r="AA96" s="229"/>
-      <c r="AB96" s="229"/>
-      <c r="AC96" s="229"/>
-      <c r="AD96" s="229"/>
-      <c r="AE96" s="229"/>
+      <c r="A96" s="247"/>
+      <c r="B96" s="247"/>
+      <c r="C96" s="247"/>
+      <c r="D96" s="247"/>
+      <c r="E96" s="247"/>
+      <c r="F96" s="247"/>
+      <c r="G96" s="247"/>
+      <c r="H96" s="247"/>
+      <c r="I96" s="247"/>
+      <c r="J96" s="247"/>
+      <c r="K96" s="247"/>
+      <c r="L96" s="247"/>
+      <c r="M96" s="247"/>
+      <c r="N96" s="247"/>
+      <c r="O96" s="247"/>
+      <c r="P96" s="247"/>
+      <c r="Q96" s="247"/>
+      <c r="R96" s="247"/>
+      <c r="S96" s="247"/>
+      <c r="T96" s="247"/>
+      <c r="U96" s="247"/>
+      <c r="V96" s="247"/>
+      <c r="W96" s="247"/>
+      <c r="X96" s="247"/>
+      <c r="Y96" s="247"/>
+      <c r="Z96" s="247"/>
+      <c r="AA96" s="247"/>
+      <c r="AB96" s="247"/>
+      <c r="AC96" s="247"/>
+      <c r="AD96" s="247"/>
+      <c r="AE96" s="247"/>
       <c r="AF96" s="150"/>
       <c r="AG96" s="150"/>
       <c r="AH96" s="150"/>
@@ -23608,7 +23370,7 @@
         <v>106</v>
       </c>
       <c r="B98" s="162"/>
-      <c r="C98" s="292" t="s">
+      <c r="C98" s="219" t="s">
         <v>107</v>
       </c>
       <c r="D98" s="163"/>
@@ -23626,7 +23388,7 @@
         <v>106</v>
       </c>
       <c r="P98" s="218"/>
-      <c r="Q98" s="219" t="s">
+      <c r="Q98" s="293" t="s">
         <v>108</v>
       </c>
       <c r="R98" s="158"/>
@@ -23660,13 +23422,11 @@
       <c r="AU98" s="160"/>
     </row>
     <row r="99" spans="1:47" s="161" customFormat="1" ht="57" customHeight="1">
-      <c r="A99" s="226" t="s">
+      <c r="A99" s="256" t="s">
         <v>109</v>
       </c>
-      <c r="B99" s="226"/>
-      <c r="C99" s="210" t="s">
-        <v>110</v>
-      </c>
+      <c r="B99" s="256"/>
+      <c r="C99" s="210"/>
       <c r="D99" s="165"/>
       <c r="E99" s="163"/>
       <c r="F99" s="163"/>
@@ -23678,11 +23438,11 @@
       <c r="L99" s="163"/>
       <c r="M99" s="158"/>
       <c r="N99" s="172"/>
-      <c r="O99" s="226" t="s">
+      <c r="O99" s="256" t="s">
         <v>109</v>
       </c>
-      <c r="P99" s="226"/>
-      <c r="Q99" s="226"/>
+      <c r="P99" s="256"/>
+      <c r="Q99" s="256"/>
       <c r="R99" s="218"/>
       <c r="S99" s="158"/>
       <c r="T99" s="158"/>
@@ -23715,12 +23475,10 @@
     </row>
     <row r="100" spans="1:47" s="161" customFormat="1" ht="50.1" customHeight="1">
       <c r="A100" s="162" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B100" s="166"/>
-      <c r="C100" s="210" t="s">
-        <v>112</v>
-      </c>
+      <c r="C100" s="210"/>
       <c r="D100" s="163"/>
       <c r="E100" s="163"/>
       <c r="F100" s="163"/>
@@ -23733,7 +23491,7 @@
       <c r="M100" s="158"/>
       <c r="N100" s="172"/>
       <c r="O100" s="166" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P100" s="158"/>
       <c r="Q100" s="158"/>
@@ -23765,7 +23523,7 @@
     </row>
     <row r="101" spans="1:47" s="161" customFormat="1" ht="50.1" customHeight="1">
       <c r="A101" s="154" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B101" s="155"/>
       <c r="C101" s="155"/>
@@ -23781,7 +23539,7 @@
       <c r="M101" s="157"/>
       <c r="N101" s="172"/>
       <c r="O101" s="155" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="P101" s="157"/>
       <c r="Q101" s="157"/>
@@ -23816,8 +23574,8 @@
         <v>106</v>
       </c>
       <c r="B102" s="162"/>
-      <c r="C102" s="292" t="s">
-        <v>115</v>
+      <c r="C102" s="219" t="s">
+        <v>113</v>
       </c>
       <c r="D102" s="166"/>
       <c r="E102" s="163"/>
@@ -23834,8 +23592,8 @@
         <v>106</v>
       </c>
       <c r="P102" s="158"/>
-      <c r="Q102" s="219" t="s">
-        <v>116</v>
+      <c r="Q102" s="293" t="s">
+        <v>114</v>
       </c>
       <c r="R102" s="158"/>
       <c r="S102" s="158"/>
@@ -23864,13 +23622,11 @@
       <c r="AU102" s="160"/>
     </row>
     <row r="103" spans="1:47" s="161" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A103" s="226" t="s">
+      <c r="A103" s="256" t="s">
         <v>109</v>
       </c>
-      <c r="B103" s="226"/>
-      <c r="C103" s="210" t="s">
-        <v>110</v>
-      </c>
+      <c r="B103" s="256"/>
+      <c r="C103" s="210"/>
       <c r="D103" s="165"/>
       <c r="E103" s="163"/>
       <c r="F103" s="163"/>
@@ -23882,12 +23638,12 @@
       <c r="L103" s="163"/>
       <c r="M103" s="158"/>
       <c r="N103" s="172"/>
-      <c r="O103" s="226" t="s">
+      <c r="O103" s="256" t="s">
         <v>109</v>
       </c>
-      <c r="P103" s="226"/>
-      <c r="Q103" s="226"/>
-      <c r="R103" s="226"/>
+      <c r="P103" s="256"/>
+      <c r="Q103" s="256"/>
+      <c r="R103" s="256"/>
       <c r="S103" s="158"/>
       <c r="T103" s="158"/>
       <c r="U103" s="158"/>
@@ -23915,12 +23671,10 @@
     </row>
     <row r="104" spans="1:47" s="161" customFormat="1" ht="50.1" customHeight="1">
       <c r="A104" s="162" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B104" s="166"/>
-      <c r="C104" s="210" t="s">
-        <v>112</v>
-      </c>
+      <c r="C104" s="210"/>
       <c r="D104" s="163"/>
       <c r="E104" s="163"/>
       <c r="F104" s="163"/>
@@ -23933,7 +23687,7 @@
       <c r="M104" s="158"/>
       <c r="N104" s="172"/>
       <c r="O104" s="166" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P104" s="158"/>
       <c r="Q104" s="158"/>
@@ -23965,7 +23719,7 @@
     </row>
     <row r="105" spans="1:47" s="161" customFormat="1" ht="50.1" customHeight="1">
       <c r="A105" s="154" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B105" s="155"/>
       <c r="C105" s="155"/>
@@ -23981,7 +23735,7 @@
       <c r="M105" s="157"/>
       <c r="N105" s="172"/>
       <c r="O105" s="155" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="P105" s="157"/>
       <c r="Q105" s="157"/>
@@ -24016,8 +23770,8 @@
         <v>106</v>
       </c>
       <c r="B106" s="162"/>
-      <c r="C106" s="292" t="s">
-        <v>119</v>
+      <c r="C106" s="219" t="s">
+        <v>117</v>
       </c>
       <c r="D106" s="166"/>
       <c r="E106" s="163"/>
@@ -24034,8 +23788,8 @@
         <v>106</v>
       </c>
       <c r="P106" s="158"/>
-      <c r="Q106" s="219" t="s">
-        <v>120</v>
+      <c r="Q106" s="293" t="s">
+        <v>118</v>
       </c>
       <c r="R106" s="158"/>
       <c r="S106" s="158"/>
@@ -24064,13 +23818,11 @@
       <c r="AU106" s="160"/>
     </row>
     <row r="107" spans="1:47" s="161" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A107" s="226" t="s">
+      <c r="A107" s="256" t="s">
         <v>109</v>
       </c>
-      <c r="B107" s="226"/>
-      <c r="C107" s="210" t="s">
-        <v>110</v>
-      </c>
+      <c r="B107" s="256"/>
+      <c r="C107" s="210"/>
       <c r="D107" s="165"/>
       <c r="E107" s="163"/>
       <c r="F107" s="163"/>
@@ -24082,11 +23834,11 @@
       <c r="L107" s="163"/>
       <c r="M107" s="158"/>
       <c r="N107" s="172"/>
-      <c r="O107" s="226" t="s">
+      <c r="O107" s="256" t="s">
         <v>109</v>
       </c>
-      <c r="P107" s="226"/>
-      <c r="Q107" s="226"/>
+      <c r="P107" s="256"/>
+      <c r="Q107" s="256"/>
       <c r="R107" s="158"/>
       <c r="S107" s="158"/>
       <c r="T107" s="158"/>
@@ -24115,12 +23867,10 @@
     </row>
     <row r="108" spans="1:47" s="161" customFormat="1" ht="50.1" customHeight="1">
       <c r="A108" s="162" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B108" s="166"/>
-      <c r="C108" s="210" t="s">
-        <v>112</v>
-      </c>
+      <c r="C108" s="210"/>
       <c r="D108" s="163"/>
       <c r="E108" s="163"/>
       <c r="F108" s="163"/>
@@ -24133,7 +23883,7 @@
       <c r="M108" s="158"/>
       <c r="N108" s="172"/>
       <c r="O108" s="166" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P108" s="158"/>
       <c r="Q108" s="158"/>
@@ -24165,7 +23915,7 @@
     </row>
     <row r="109" spans="1:47" s="161" customFormat="1" ht="50.1" customHeight="1">
       <c r="A109" s="154" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B109" s="155"/>
       <c r="C109" s="155"/>
@@ -24181,7 +23931,7 @@
       <c r="M109" s="157"/>
       <c r="N109" s="172"/>
       <c r="O109" s="155" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="P109" s="157"/>
       <c r="Q109" s="157"/>
@@ -24216,8 +23966,8 @@
         <v>106</v>
       </c>
       <c r="B110" s="162"/>
-      <c r="C110" s="292" t="s">
-        <v>123</v>
+      <c r="C110" s="219" t="s">
+        <v>121</v>
       </c>
       <c r="D110" s="166"/>
       <c r="E110" s="163"/>
@@ -24234,8 +23984,8 @@
         <v>106</v>
       </c>
       <c r="P110" s="158"/>
-      <c r="Q110" s="219" t="s">
-        <v>124</v>
+      <c r="Q110" s="293" t="s">
+        <v>122</v>
       </c>
       <c r="R110" s="158"/>
       <c r="S110" s="158"/>
@@ -24264,13 +24014,11 @@
       <c r="AU110" s="160"/>
     </row>
     <row r="111" spans="1:47" s="161" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A111" s="226" t="s">
+      <c r="A111" s="256" t="s">
         <v>109</v>
       </c>
-      <c r="B111" s="226"/>
-      <c r="C111" s="210" t="s">
-        <v>125</v>
-      </c>
+      <c r="B111" s="256"/>
+      <c r="C111" s="210"/>
       <c r="D111" s="165"/>
       <c r="E111" s="163"/>
       <c r="F111" s="163"/>
@@ -24282,11 +24030,11 @@
       <c r="L111" s="163"/>
       <c r="M111" s="158"/>
       <c r="N111" s="172"/>
-      <c r="O111" s="226" t="s">
+      <c r="O111" s="256" t="s">
         <v>109</v>
       </c>
-      <c r="P111" s="226"/>
-      <c r="Q111" s="226"/>
+      <c r="P111" s="256"/>
+      <c r="Q111" s="256"/>
       <c r="R111" s="158"/>
       <c r="S111" s="158"/>
       <c r="T111" s="158"/>
@@ -24315,12 +24063,10 @@
     </row>
     <row r="112" spans="1:47" s="161" customFormat="1" ht="50.1" customHeight="1">
       <c r="A112" s="162" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B112" s="166"/>
-      <c r="C112" s="210" t="s">
-        <v>126</v>
-      </c>
+      <c r="C112" s="210"/>
       <c r="D112" s="163"/>
       <c r="E112" s="163"/>
       <c r="F112" s="163"/>
@@ -24333,7 +24079,7 @@
       <c r="M112" s="158"/>
       <c r="N112" s="172"/>
       <c r="O112" s="166" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P112" s="158"/>
       <c r="Q112" s="158"/>
@@ -24365,7 +24111,7 @@
     </row>
     <row r="113" spans="1:47" s="161" customFormat="1" ht="50.1" customHeight="1">
       <c r="A113" s="154" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B113" s="155"/>
       <c r="C113" s="155"/>
@@ -24381,7 +24127,7 @@
       <c r="M113" s="157"/>
       <c r="N113" s="172"/>
       <c r="O113" s="155" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="P113" s="157"/>
       <c r="Q113" s="157"/>
@@ -24416,8 +24162,8 @@
         <v>106</v>
       </c>
       <c r="B114" s="162"/>
-      <c r="C114" s="292" t="s">
-        <v>129</v>
+      <c r="C114" s="219" t="s">
+        <v>125</v>
       </c>
       <c r="D114" s="166"/>
       <c r="E114" s="163"/>
@@ -24434,8 +24180,8 @@
         <v>106</v>
       </c>
       <c r="P114" s="158"/>
-      <c r="Q114" s="219" t="s">
-        <v>130</v>
+      <c r="Q114" s="293" t="s">
+        <v>126</v>
       </c>
       <c r="R114" s="158"/>
       <c r="S114" s="158"/>
@@ -24464,13 +24210,11 @@
       <c r="AU114" s="160"/>
     </row>
     <row r="115" spans="1:47" s="161" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A115" s="226" t="s">
+      <c r="A115" s="256" t="s">
         <v>109</v>
       </c>
-      <c r="B115" s="226"/>
-      <c r="C115" s="210" t="s">
-        <v>110</v>
-      </c>
+      <c r="B115" s="256"/>
+      <c r="C115" s="210"/>
       <c r="D115" s="163"/>
       <c r="E115" s="163"/>
       <c r="F115" s="163"/>
@@ -24482,11 +24226,11 @@
       <c r="L115" s="163"/>
       <c r="M115" s="158"/>
       <c r="N115" s="172"/>
-      <c r="O115" s="226" t="s">
+      <c r="O115" s="256" t="s">
         <v>109</v>
       </c>
-      <c r="P115" s="226"/>
-      <c r="Q115" s="226"/>
+      <c r="P115" s="256"/>
+      <c r="Q115" s="256"/>
       <c r="R115" s="158"/>
       <c r="S115" s="158"/>
       <c r="T115" s="158"/>
@@ -24515,12 +24259,10 @@
     </row>
     <row r="116" spans="1:47" s="161" customFormat="1" ht="50.1" customHeight="1">
       <c r="A116" s="162" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B116" s="166"/>
-      <c r="C116" s="210" t="s">
-        <v>112</v>
-      </c>
+      <c r="C116" s="210"/>
       <c r="D116" s="163"/>
       <c r="E116" s="163"/>
       <c r="F116" s="163"/>
@@ -24533,7 +24275,7 @@
       <c r="M116" s="158"/>
       <c r="N116" s="172"/>
       <c r="O116" s="166" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P116" s="158"/>
       <c r="Q116" s="158"/>
@@ -24565,7 +24307,7 @@
     </row>
     <row r="117" spans="1:47" s="161" customFormat="1" ht="50.1" customHeight="1">
       <c r="A117" s="154" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B117" s="155"/>
       <c r="C117" s="155"/>
@@ -24581,7 +24323,7 @@
       <c r="M117" s="157"/>
       <c r="N117" s="172"/>
       <c r="O117" s="155" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="P117" s="157"/>
       <c r="Q117" s="157"/>
@@ -24616,8 +24358,8 @@
         <v>106</v>
       </c>
       <c r="B118" s="162"/>
-      <c r="C118" s="292" t="s">
-        <v>133</v>
+      <c r="C118" s="219" t="s">
+        <v>129</v>
       </c>
       <c r="D118" s="166"/>
       <c r="E118" s="163"/>
@@ -24634,8 +24376,8 @@
         <v>106</v>
       </c>
       <c r="P118" s="158"/>
-      <c r="Q118" s="219" t="s">
-        <v>134</v>
+      <c r="Q118" s="293" t="s">
+        <v>130</v>
       </c>
       <c r="R118" s="158"/>
       <c r="S118" s="158"/>
@@ -24664,12 +24406,12 @@
       <c r="AU118" s="160"/>
     </row>
     <row r="119" spans="1:47" s="161" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A119" s="226" t="s">
+      <c r="A119" s="256" t="s">
         <v>109</v>
       </c>
-      <c r="B119" s="226"/>
+      <c r="B119" s="256"/>
       <c r="C119" s="210" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="D119" s="165"/>
       <c r="E119" s="163"/>
@@ -24682,11 +24424,11 @@
       <c r="L119" s="163"/>
       <c r="M119" s="158"/>
       <c r="N119" s="172"/>
-      <c r="O119" s="226" t="s">
+      <c r="O119" s="256" t="s">
         <v>109</v>
       </c>
-      <c r="P119" s="226"/>
-      <c r="Q119" s="226"/>
+      <c r="P119" s="256"/>
+      <c r="Q119" s="256"/>
       <c r="R119" s="158"/>
       <c r="S119" s="158"/>
       <c r="T119" s="158"/>
@@ -24715,11 +24457,11 @@
     </row>
     <row r="120" spans="1:47" s="161" customFormat="1" ht="50.1" customHeight="1">
       <c r="A120" s="162" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B120" s="166"/>
       <c r="C120" s="210" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="D120" s="163"/>
       <c r="E120" s="167"/>
@@ -24733,7 +24475,7 @@
       <c r="M120" s="158"/>
       <c r="N120" s="172"/>
       <c r="O120" s="166" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P120" s="158"/>
       <c r="Q120" s="158"/>
@@ -24764,39 +24506,39 @@
       <c r="AU120" s="160"/>
     </row>
     <row r="121" spans="1:47" s="151" customFormat="1" ht="30" customHeight="1">
-      <c r="A121" s="293" t="s">
-        <v>135</v>
-      </c>
-      <c r="B121" s="225"/>
-      <c r="C121" s="225"/>
-      <c r="D121" s="225"/>
-      <c r="E121" s="225"/>
-      <c r="F121" s="225"/>
-      <c r="G121" s="225"/>
-      <c r="H121" s="225"/>
-      <c r="I121" s="225"/>
-      <c r="J121" s="225"/>
-      <c r="K121" s="225"/>
-      <c r="L121" s="225"/>
-      <c r="M121" s="225"/>
-      <c r="N121" s="225"/>
-      <c r="O121" s="225"/>
-      <c r="P121" s="225"/>
-      <c r="Q121" s="225"/>
-      <c r="R121" s="225"/>
-      <c r="S121" s="225"/>
-      <c r="T121" s="225"/>
-      <c r="U121" s="225"/>
-      <c r="V121" s="225"/>
-      <c r="W121" s="225"/>
-      <c r="X121" s="225"/>
-      <c r="Y121" s="225"/>
-      <c r="Z121" s="225"/>
-      <c r="AA121" s="225"/>
-      <c r="AB121" s="225"/>
-      <c r="AC121" s="225"/>
-      <c r="AD121" s="225"/>
-      <c r="AE121" s="225"/>
+      <c r="A121" s="254" t="s">
+        <v>133</v>
+      </c>
+      <c r="B121" s="255"/>
+      <c r="C121" s="255"/>
+      <c r="D121" s="255"/>
+      <c r="E121" s="255"/>
+      <c r="F121" s="255"/>
+      <c r="G121" s="255"/>
+      <c r="H121" s="255"/>
+      <c r="I121" s="255"/>
+      <c r="J121" s="255"/>
+      <c r="K121" s="255"/>
+      <c r="L121" s="255"/>
+      <c r="M121" s="255"/>
+      <c r="N121" s="255"/>
+      <c r="O121" s="255"/>
+      <c r="P121" s="255"/>
+      <c r="Q121" s="255"/>
+      <c r="R121" s="255"/>
+      <c r="S121" s="255"/>
+      <c r="T121" s="255"/>
+      <c r="U121" s="255"/>
+      <c r="V121" s="255"/>
+      <c r="W121" s="255"/>
+      <c r="X121" s="255"/>
+      <c r="Y121" s="255"/>
+      <c r="Z121" s="255"/>
+      <c r="AA121" s="255"/>
+      <c r="AB121" s="255"/>
+      <c r="AC121" s="255"/>
+      <c r="AD121" s="255"/>
+      <c r="AE121" s="255"/>
       <c r="AF121" s="150"/>
       <c r="AG121" s="150"/>
       <c r="AH121" s="150"/>
@@ -24814,37 +24556,37 @@
       <c r="AU121" s="152"/>
     </row>
     <row r="122" spans="1:47" s="151" customFormat="1" ht="30" customHeight="1">
-      <c r="A122" s="225"/>
-      <c r="B122" s="225"/>
-      <c r="C122" s="225"/>
-      <c r="D122" s="225"/>
-      <c r="E122" s="225"/>
-      <c r="F122" s="225"/>
-      <c r="G122" s="225"/>
-      <c r="H122" s="225"/>
-      <c r="I122" s="225"/>
-      <c r="J122" s="225"/>
-      <c r="K122" s="225"/>
-      <c r="L122" s="225"/>
-      <c r="M122" s="225"/>
-      <c r="N122" s="225"/>
-      <c r="O122" s="225"/>
-      <c r="P122" s="225"/>
-      <c r="Q122" s="225"/>
-      <c r="R122" s="225"/>
-      <c r="S122" s="225"/>
-      <c r="T122" s="225"/>
-      <c r="U122" s="225"/>
-      <c r="V122" s="225"/>
-      <c r="W122" s="225"/>
-      <c r="X122" s="225"/>
-      <c r="Y122" s="225"/>
-      <c r="Z122" s="225"/>
-      <c r="AA122" s="225"/>
-      <c r="AB122" s="225"/>
-      <c r="AC122" s="225"/>
-      <c r="AD122" s="225"/>
-      <c r="AE122" s="225"/>
+      <c r="A122" s="255"/>
+      <c r="B122" s="255"/>
+      <c r="C122" s="255"/>
+      <c r="D122" s="255"/>
+      <c r="E122" s="255"/>
+      <c r="F122" s="255"/>
+      <c r="G122" s="255"/>
+      <c r="H122" s="255"/>
+      <c r="I122" s="255"/>
+      <c r="J122" s="255"/>
+      <c r="K122" s="255"/>
+      <c r="L122" s="255"/>
+      <c r="M122" s="255"/>
+      <c r="N122" s="255"/>
+      <c r="O122" s="255"/>
+      <c r="P122" s="255"/>
+      <c r="Q122" s="255"/>
+      <c r="R122" s="255"/>
+      <c r="S122" s="255"/>
+      <c r="T122" s="255"/>
+      <c r="U122" s="255"/>
+      <c r="V122" s="255"/>
+      <c r="W122" s="255"/>
+      <c r="X122" s="255"/>
+      <c r="Y122" s="255"/>
+      <c r="Z122" s="255"/>
+      <c r="AA122" s="255"/>
+      <c r="AB122" s="255"/>
+      <c r="AC122" s="255"/>
+      <c r="AD122" s="255"/>
+      <c r="AE122" s="255"/>
       <c r="AM122" s="152"/>
       <c r="AN122" s="152"/>
       <c r="AO122" s="152"/>
@@ -24855,37 +24597,37 @@
       <c r="AU122" s="152"/>
     </row>
     <row r="123" spans="1:47" s="151" customFormat="1" ht="30" customHeight="1">
-      <c r="A123" s="225"/>
-      <c r="B123" s="225"/>
-      <c r="C123" s="225"/>
-      <c r="D123" s="225"/>
-      <c r="E123" s="225"/>
-      <c r="F123" s="225"/>
-      <c r="G123" s="225"/>
-      <c r="H123" s="225"/>
-      <c r="I123" s="225"/>
-      <c r="J123" s="225"/>
-      <c r="K123" s="225"/>
-      <c r="L123" s="225"/>
-      <c r="M123" s="225"/>
-      <c r="N123" s="225"/>
-      <c r="O123" s="225"/>
-      <c r="P123" s="225"/>
-      <c r="Q123" s="225"/>
-      <c r="R123" s="225"/>
-      <c r="S123" s="225"/>
-      <c r="T123" s="225"/>
-      <c r="U123" s="225"/>
-      <c r="V123" s="225"/>
-      <c r="W123" s="225"/>
-      <c r="X123" s="225"/>
-      <c r="Y123" s="225"/>
-      <c r="Z123" s="225"/>
-      <c r="AA123" s="225"/>
-      <c r="AB123" s="225"/>
-      <c r="AC123" s="225"/>
-      <c r="AD123" s="225"/>
-      <c r="AE123" s="225"/>
+      <c r="A123" s="255"/>
+      <c r="B123" s="255"/>
+      <c r="C123" s="255"/>
+      <c r="D123" s="255"/>
+      <c r="E123" s="255"/>
+      <c r="F123" s="255"/>
+      <c r="G123" s="255"/>
+      <c r="H123" s="255"/>
+      <c r="I123" s="255"/>
+      <c r="J123" s="255"/>
+      <c r="K123" s="255"/>
+      <c r="L123" s="255"/>
+      <c r="M123" s="255"/>
+      <c r="N123" s="255"/>
+      <c r="O123" s="255"/>
+      <c r="P123" s="255"/>
+      <c r="Q123" s="255"/>
+      <c r="R123" s="255"/>
+      <c r="S123" s="255"/>
+      <c r="T123" s="255"/>
+      <c r="U123" s="255"/>
+      <c r="V123" s="255"/>
+      <c r="W123" s="255"/>
+      <c r="X123" s="255"/>
+      <c r="Y123" s="255"/>
+      <c r="Z123" s="255"/>
+      <c r="AA123" s="255"/>
+      <c r="AB123" s="255"/>
+      <c r="AC123" s="255"/>
+      <c r="AD123" s="255"/>
+      <c r="AE123" s="255"/>
       <c r="AG123" s="152"/>
       <c r="AH123" s="152"/>
       <c r="AI123" s="152"/>
@@ -24903,6 +24645,50 @@
     </row>
   </sheetData>
   <mergeCells count="60">
+    <mergeCell ref="A121:AE123"/>
+    <mergeCell ref="A99:B99"/>
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="A107:B107"/>
+    <mergeCell ref="A111:B111"/>
+    <mergeCell ref="A115:B115"/>
+    <mergeCell ref="A119:B119"/>
+    <mergeCell ref="O99:Q99"/>
+    <mergeCell ref="O103:R103"/>
+    <mergeCell ref="O107:Q107"/>
+    <mergeCell ref="O111:Q111"/>
+    <mergeCell ref="O115:Q115"/>
+    <mergeCell ref="O119:Q119"/>
+    <mergeCell ref="C49:Q50"/>
+    <mergeCell ref="A95:AE96"/>
+    <mergeCell ref="B3:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="A6:A19"/>
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="AC4:AD4"/>
+    <mergeCell ref="A21:A25"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
     <mergeCell ref="A2:AE2"/>
     <mergeCell ref="M4:N4"/>
     <mergeCell ref="O4:P4"/>
@@ -24919,50 +24705,6 @@
     <mergeCell ref="W4:X4"/>
     <mergeCell ref="AE4:AE5"/>
     <mergeCell ref="AA4:AB4"/>
-    <mergeCell ref="AC4:AD4"/>
-    <mergeCell ref="A21:A25"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="C49:Q50"/>
-    <mergeCell ref="A95:AE96"/>
-    <mergeCell ref="B3:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="A6:A19"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="A121:AE123"/>
-    <mergeCell ref="A99:B99"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="A107:B107"/>
-    <mergeCell ref="A111:B111"/>
-    <mergeCell ref="A115:B115"/>
-    <mergeCell ref="A119:B119"/>
-    <mergeCell ref="O99:Q99"/>
-    <mergeCell ref="O103:R103"/>
-    <mergeCell ref="O107:Q107"/>
-    <mergeCell ref="O111:Q111"/>
-    <mergeCell ref="O115:Q115"/>
-    <mergeCell ref="O119:Q119"/>
   </mergeCells>
   <phoneticPr fontId="29" type="noConversion"/>
   <pageMargins left="0.44" right="0.2" top="0.33" bottom="0.31" header="0.26" footer="0.31496062992125984"/>
@@ -25000,93 +24742,93 @@
       </c>
     </row>
     <row r="2" spans="1:31" ht="24.95" customHeight="1">
-      <c r="A2" s="267" t="s">
+      <c r="A2" s="257" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="268"/>
-      <c r="C2" s="268"/>
-      <c r="D2" s="268"/>
-      <c r="E2" s="268"/>
-      <c r="F2" s="268"/>
-      <c r="G2" s="268"/>
-      <c r="H2" s="268"/>
-      <c r="I2" s="268"/>
-      <c r="J2" s="268"/>
-      <c r="K2" s="268"/>
-      <c r="L2" s="268"/>
-      <c r="M2" s="268"/>
-      <c r="N2" s="268"/>
-      <c r="O2" s="268"/>
-      <c r="P2" s="268"/>
-      <c r="Q2" s="268"/>
-      <c r="R2" s="268"/>
-      <c r="S2" s="268"/>
-      <c r="T2" s="268"/>
-      <c r="U2" s="268"/>
-      <c r="V2" s="268"/>
-      <c r="W2" s="268"/>
-      <c r="X2" s="268"/>
-      <c r="Y2" s="268"/>
-      <c r="Z2" s="268"/>
-      <c r="AA2" s="268"/>
-      <c r="AB2" s="268"/>
-      <c r="AC2" s="268"/>
-      <c r="AD2" s="268"/>
-      <c r="AE2" s="269"/>
+      <c r="B2" s="258"/>
+      <c r="C2" s="258"/>
+      <c r="D2" s="258"/>
+      <c r="E2" s="258"/>
+      <c r="F2" s="258"/>
+      <c r="G2" s="258"/>
+      <c r="H2" s="258"/>
+      <c r="I2" s="258"/>
+      <c r="J2" s="258"/>
+      <c r="K2" s="258"/>
+      <c r="L2" s="258"/>
+      <c r="M2" s="258"/>
+      <c r="N2" s="258"/>
+      <c r="O2" s="258"/>
+      <c r="P2" s="258"/>
+      <c r="Q2" s="258"/>
+      <c r="R2" s="258"/>
+      <c r="S2" s="258"/>
+      <c r="T2" s="258"/>
+      <c r="U2" s="258"/>
+      <c r="V2" s="258"/>
+      <c r="W2" s="258"/>
+      <c r="X2" s="258"/>
+      <c r="Y2" s="258"/>
+      <c r="Z2" s="258"/>
+      <c r="AA2" s="258"/>
+      <c r="AB2" s="258"/>
+      <c r="AC2" s="258"/>
+      <c r="AD2" s="258"/>
+      <c r="AE2" s="259"/>
     </row>
     <row r="3" spans="1:31" s="34" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A3" s="270" t="s">
+      <c r="A3" s="260" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="270" t="s">
+      <c r="B3" s="260" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="270" t="s">
+      <c r="C3" s="260" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="270" t="s">
+      <c r="D3" s="260" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="270" t="s">
-        <v>136</v>
-      </c>
-      <c r="F3" s="271" t="s">
-        <v>137</v>
-      </c>
-      <c r="G3" s="272"/>
-      <c r="H3" s="272"/>
-      <c r="I3" s="272"/>
-      <c r="J3" s="272"/>
-      <c r="K3" s="272"/>
-      <c r="L3" s="272"/>
-      <c r="M3" s="272"/>
-      <c r="N3" s="272"/>
-      <c r="O3" s="272"/>
-      <c r="P3" s="272"/>
-      <c r="Q3" s="272"/>
-      <c r="R3" s="272"/>
-      <c r="S3" s="272"/>
-      <c r="T3" s="272"/>
-      <c r="U3" s="272"/>
-      <c r="V3" s="272"/>
-      <c r="W3" s="272"/>
-      <c r="X3" s="272"/>
-      <c r="Y3" s="272"/>
-      <c r="Z3" s="272"/>
-      <c r="AA3" s="272"/>
-      <c r="AB3" s="272"/>
-      <c r="AC3" s="272"/>
-      <c r="AD3" s="272"/>
-      <c r="AE3" s="273" t="s">
+      <c r="E3" s="260" t="s">
+        <v>134</v>
+      </c>
+      <c r="F3" s="261" t="s">
+        <v>135</v>
+      </c>
+      <c r="G3" s="262"/>
+      <c r="H3" s="262"/>
+      <c r="I3" s="262"/>
+      <c r="J3" s="262"/>
+      <c r="K3" s="262"/>
+      <c r="L3" s="262"/>
+      <c r="M3" s="262"/>
+      <c r="N3" s="262"/>
+      <c r="O3" s="262"/>
+      <c r="P3" s="262"/>
+      <c r="Q3" s="262"/>
+      <c r="R3" s="262"/>
+      <c r="S3" s="262"/>
+      <c r="T3" s="262"/>
+      <c r="U3" s="262"/>
+      <c r="V3" s="262"/>
+      <c r="W3" s="262"/>
+      <c r="X3" s="262"/>
+      <c r="Y3" s="262"/>
+      <c r="Z3" s="262"/>
+      <c r="AA3" s="262"/>
+      <c r="AB3" s="262"/>
+      <c r="AC3" s="262"/>
+      <c r="AD3" s="262"/>
+      <c r="AE3" s="263" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:31" s="34" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A4" s="270"/>
-      <c r="B4" s="270"/>
-      <c r="C4" s="270"/>
-      <c r="D4" s="270"/>
-      <c r="E4" s="270"/>
+      <c r="A4" s="260"/>
+      <c r="B4" s="260"/>
+      <c r="C4" s="260"/>
+      <c r="D4" s="260"/>
+      <c r="E4" s="260"/>
       <c r="F4" s="266" t="s">
         <v>8</v>
       </c>
@@ -25135,17 +24877,17 @@
         <v>19</v>
       </c>
       <c r="AC4" s="266"/>
-      <c r="AD4" s="276" t="s">
+      <c r="AD4" s="267" t="s">
         <v>20</v>
       </c>
-      <c r="AE4" s="274"/>
+      <c r="AE4" s="264"/>
     </row>
     <row r="5" spans="1:31" s="34" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A5" s="270"/>
-      <c r="B5" s="270"/>
-      <c r="C5" s="270"/>
-      <c r="D5" s="270"/>
-      <c r="E5" s="270"/>
+      <c r="A5" s="260"/>
+      <c r="B5" s="260"/>
+      <c r="C5" s="260"/>
+      <c r="D5" s="260"/>
+      <c r="E5" s="260"/>
       <c r="F5" s="52" t="s">
         <v>21</v>
       </c>
@@ -25218,11 +24960,11 @@
       <c r="AC5" s="52" t="s">
         <v>22</v>
       </c>
-      <c r="AD5" s="277"/>
-      <c r="AE5" s="275"/>
+      <c r="AD5" s="268"/>
+      <c r="AE5" s="265"/>
     </row>
     <row r="6" spans="1:31" ht="24.95" customHeight="1">
-      <c r="A6" s="261" t="s">
+      <c r="A6" s="269" t="s">
         <v>23</v>
       </c>
       <c r="B6" s="37" t="s">
@@ -25259,7 +25001,7 @@
       <c r="AE6" s="36"/>
     </row>
     <row r="7" spans="1:31" ht="24.95" customHeight="1">
-      <c r="A7" s="262"/>
+      <c r="A7" s="270"/>
       <c r="B7" s="37" t="s">
         <v>25</v>
       </c>
@@ -25294,7 +25036,7 @@
       <c r="AE7" s="33"/>
     </row>
     <row r="8" spans="1:31" ht="24.95" customHeight="1">
-      <c r="A8" s="262"/>
+      <c r="A8" s="270"/>
       <c r="B8" s="41" t="s">
         <v>26</v>
       </c>
@@ -25396,11 +25138,11 @@
         <v>0</v>
       </c>
       <c r="AE8" s="36" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:31" ht="24.95" customHeight="1">
-      <c r="A9" s="262"/>
+      <c r="A9" s="270"/>
       <c r="B9" s="41" t="s">
         <v>29</v>
       </c>
@@ -25502,11 +25244,11 @@
         <v>0</v>
       </c>
       <c r="AE9" s="36" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="1:31" ht="24.95" customHeight="1">
-      <c r="A10" s="262"/>
+      <c r="A10" s="270"/>
       <c r="B10" s="43" t="s">
         <v>30</v>
       </c>
@@ -25541,7 +25283,7 @@
       <c r="AE10" s="36"/>
     </row>
     <row r="11" spans="1:31" ht="24.95" customHeight="1">
-      <c r="A11" s="262"/>
+      <c r="A11" s="270"/>
       <c r="B11" s="43" t="s">
         <v>31</v>
       </c>
@@ -25576,7 +25318,7 @@
       <c r="AE11" s="36"/>
     </row>
     <row r="12" spans="1:31" ht="24.95" customHeight="1">
-      <c r="A12" s="262"/>
+      <c r="A12" s="270"/>
       <c r="B12" s="41" t="s">
         <v>32</v>
       </c>
@@ -25678,11 +25420,11 @@
         <v>1906.9642920000003</v>
       </c>
       <c r="AE12" s="36" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:31" ht="24.95" customHeight="1">
-      <c r="A13" s="262"/>
+      <c r="A13" s="270"/>
       <c r="B13" s="41" t="s">
         <v>33</v>
       </c>
@@ -25784,11 +25526,11 @@
         <v>0</v>
       </c>
       <c r="AE13" s="36" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:31" ht="24.95" customHeight="1">
-      <c r="A14" s="262"/>
+      <c r="A14" s="270"/>
       <c r="B14" s="41" t="s">
         <v>34</v>
       </c>
@@ -25890,11 +25632,11 @@
         <v>0</v>
       </c>
       <c r="AE14" s="36" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15" spans="1:31" ht="24.95" customHeight="1">
-      <c r="A15" s="262"/>
+      <c r="A15" s="270"/>
       <c r="B15" s="43" t="s">
         <v>35</v>
       </c>
@@ -25996,11 +25738,11 @@
         <v>0</v>
       </c>
       <c r="AE15" s="36" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16" spans="1:31" ht="24.6" customHeight="1">
-      <c r="A16" s="262"/>
+      <c r="A16" s="270"/>
       <c r="B16" s="60" t="s">
         <v>38</v>
       </c>
@@ -26078,11 +25820,11 @@
         <v>0</v>
       </c>
       <c r="AE16" s="36" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" spans="1:44" ht="24.6" customHeight="1">
-      <c r="A17" s="262"/>
+      <c r="A17" s="270"/>
       <c r="B17" s="61" t="s">
         <v>41</v>
       </c>
@@ -26160,11 +25902,11 @@
         <v>0</v>
       </c>
       <c r="AE17" s="36" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="18" spans="1:44" ht="24.6" customHeight="1">
-      <c r="A18" s="262"/>
+      <c r="A18" s="270"/>
       <c r="B18" s="43" t="s">
         <v>42</v>
       </c>
@@ -26205,7 +25947,7 @@
       <c r="AE18" s="36"/>
     </row>
     <row r="19" spans="1:44" ht="24.95" customHeight="1">
-      <c r="A19" s="263"/>
+      <c r="A19" s="271"/>
       <c r="B19" s="43" t="s">
         <v>45</v>
       </c>
@@ -26307,7 +26049,7 @@
         <v>0</v>
       </c>
       <c r="AE19" s="36" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20" spans="1:44" ht="36.950000000000003" customHeight="1">
@@ -26415,11 +26157,11 @@
         <v>201478.09632000004</v>
       </c>
       <c r="AE20" s="36" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="21" spans="1:44" ht="24.95" customHeight="1">
-      <c r="A21" s="261" t="s">
+      <c r="A21" s="269" t="s">
         <v>52</v>
       </c>
       <c r="B21" s="41" t="s">
@@ -26523,11 +26265,11 @@
         <v>4619.775599999999</v>
       </c>
       <c r="AE21" s="36" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="22" spans="1:44" ht="24.95" customHeight="1">
-      <c r="A22" s="262"/>
+      <c r="A22" s="270"/>
       <c r="B22" s="41" t="s">
         <v>55</v>
       </c>
@@ -26629,11 +26371,11 @@
         <v>0</v>
       </c>
       <c r="AE22" s="36" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="23" spans="1:44" ht="24.95" customHeight="1">
-      <c r="A23" s="262"/>
+      <c r="A23" s="270"/>
       <c r="B23" s="41" t="s">
         <v>58</v>
       </c>
@@ -26735,12 +26477,12 @@
         <v>4510.5874999999996</v>
       </c>
       <c r="AE23" s="36" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AR23" s="45"/>
     </row>
     <row r="24" spans="1:44" ht="24.95" customHeight="1">
-      <c r="A24" s="262"/>
+      <c r="A24" s="270"/>
       <c r="B24" s="39" t="s">
         <v>59</v>
       </c>
@@ -26842,12 +26584,12 @@
         <v>10163.92</v>
       </c>
       <c r="AE24" s="36" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AR24" s="47"/>
     </row>
     <row r="25" spans="1:44" ht="25.5" customHeight="1">
-      <c r="A25" s="263"/>
+      <c r="A25" s="271"/>
       <c r="B25" s="115" t="s">
         <v>60</v>
       </c>
@@ -26949,18 +26691,18 @@
         <v>0</v>
       </c>
       <c r="AE25" s="36" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AR25" s="47"/>
     </row>
     <row r="26" spans="1:44" ht="25.5" customHeight="1">
-      <c r="A26" s="264" t="s">
+      <c r="A26" s="272" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="264"/>
-      <c r="C26" s="264"/>
-      <c r="D26" s="264"/>
-      <c r="E26" s="264"/>
+      <c r="B26" s="272"/>
+      <c r="C26" s="272"/>
+      <c r="D26" s="272"/>
+      <c r="E26" s="272"/>
       <c r="F26" s="133"/>
       <c r="G26" s="134">
         <f t="shared" ref="G26:AD26" si="13">SUM(G8:G25)</f>
@@ -27026,7 +26768,7 @@
         <v>222679.34371200003</v>
       </c>
       <c r="AE26" s="36" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AR26" s="47"/>
     </row>
@@ -27072,7 +26814,7 @@
     </row>
     <row r="30" spans="1:44" ht="24.95" customHeight="1">
       <c r="B30" s="116" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="K30" s="45"/>
       <c r="L30" s="45"/>
@@ -27151,12 +26893,12 @@
       <c r="AW35" s="46"/>
     </row>
     <row r="36" spans="1:49" ht="24.95" customHeight="1">
-      <c r="B36" s="265" t="s">
-        <v>140</v>
-      </c>
-      <c r="C36" s="265"/>
-      <c r="D36" s="265"/>
-      <c r="E36" s="265"/>
+      <c r="B36" s="273" t="s">
+        <v>138</v>
+      </c>
+      <c r="C36" s="273"/>
+      <c r="D36" s="273"/>
+      <c r="E36" s="273"/>
       <c r="J36" s="32"/>
       <c r="AW36" s="46"/>
     </row>
@@ -27165,10 +26907,10 @@
         <v>73</v>
       </c>
       <c r="C37" s="117" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D37" s="117" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E37" s="117" t="s">
         <v>5</v>
@@ -27189,7 +26931,7 @@
         <v>0.85637233351394837</v>
       </c>
       <c r="E38" s="118" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="J38" s="32"/>
       <c r="AW38" s="46"/>
@@ -27207,7 +26949,7 @@
         <v>90.479023766380223</v>
       </c>
       <c r="E39" s="118" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="J39" s="32"/>
       <c r="AW39" s="46"/>
@@ -27225,7 +26967,7 @@
         <v>8.6646039001058206</v>
       </c>
       <c r="E40" s="118" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="J40" s="32"/>
       <c r="AW40" s="46"/>
@@ -27244,7 +26986,7 @@
         <v>100</v>
       </c>
       <c r="E41" s="118" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="J41" s="32"/>
       <c r="AW41" s="46"/>
@@ -27284,6 +27026,16 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="A21:A25"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="X4:Y4"/>
+    <mergeCell ref="A6:A19"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="P4:Q4"/>
     <mergeCell ref="A2:AE2"/>
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="B3:B5"/>
@@ -27299,16 +27051,6 @@
     <mergeCell ref="AD4:AD5"/>
     <mergeCell ref="R4:S4"/>
     <mergeCell ref="T4:U4"/>
-    <mergeCell ref="A21:A25"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="B36:E36"/>
-    <mergeCell ref="V4:W4"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="A6:A19"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="P4:Q4"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="37" orientation="landscape" r:id="rId1"/>
@@ -27334,57 +27076,57 @@
   <sheetData>
     <row r="1" spans="1:18" ht="29.25">
       <c r="A1" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="O1" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="Q1" s="22" t="s">
         <v>157</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="Q1" s="22" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="29.25">
       <c r="B2" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C2" s="19"/>
       <c r="D2" s="19"/>
@@ -27407,12 +27149,12 @@
         <v>1.2E-2</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="B3" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C3" s="19">
         <v>95</v>
@@ -27458,7 +27200,7 @@
     </row>
     <row r="4" spans="1:18">
       <c r="B4" s="30" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C4" s="20">
         <f>C2*C3*$Q$2</f>
@@ -27515,7 +27257,7 @@
     </row>
     <row r="5" spans="1:18">
       <c r="B5" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -27533,50 +27275,50 @@
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="96">
       <c r="A10" s="10" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="72">
       <c r="A12" s="10" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="54.75" customHeight="1">
       <c r="A14" s="10" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="72">
       <c r="D22" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="F22" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="E22" s="11" t="s">
+      <c r="G22" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="F22" s="11" t="s">
+      <c r="H22" s="12" t="s">
         <v>171</v>
-      </c>
-      <c r="G22" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="H22" s="12" t="s">
-        <v>173</v>
       </c>
       <c r="I22" s="13">
         <v>1E-3</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="31" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B23" s="14" t="s">
         <v>37</v>
@@ -27640,14 +27382,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" s="278" t="s">
-        <v>175</v>
-      </c>
-      <c r="B1" s="279"/>
+      <c r="A1" s="274" t="s">
+        <v>173</v>
+      </c>
+      <c r="B1" s="275"/>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="279"/>
-      <c r="B2" s="279"/>
+      <c r="A2" s="275"/>
+      <c r="B2" s="275"/>
       <c r="C2" s="16" t="s">
         <v>8</v>
       </c>
@@ -27690,7 +27432,7 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C3" s="173"/>
       <c r="D3" s="173"/>
@@ -27708,7 +27450,7 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C4" s="27">
         <f>C3*0.8</f>
@@ -27765,42 +27507,42 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="6" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="28" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H7" s="53">
         <v>0.05</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="L7" s="11"/>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="24" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="24" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="24" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="23" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B11" s="25" t="s">
         <v>8</v>
@@ -27844,7 +27586,7 @@
     </row>
     <row r="12" spans="1:16">
       <c r="A12" s="6" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B12" s="27">
         <f t="shared" ref="B12:N12" si="1">C4</f>
@@ -27901,7 +27643,7 @@
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="29" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B13" s="26">
         <f t="shared" ref="B13:N13" si="2">$H$7*B12*0.12</f>
@@ -27958,51 +27700,51 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="6" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A15" s="276" t="s">
+        <v>187</v>
+      </c>
+      <c r="B15" s="276"/>
+      <c r="C15" s="276"/>
+      <c r="D15" s="276"/>
+      <c r="E15" s="276"/>
+      <c r="F15" s="276"/>
+      <c r="G15" s="276"/>
+      <c r="H15" s="276"/>
+      <c r="I15" s="276"/>
+      <c r="J15" s="276"/>
+      <c r="K15" s="276"/>
+      <c r="L15" s="276"/>
+      <c r="M15" s="276"/>
+      <c r="N15" s="276"/>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16" s="276" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" ht="25.5" customHeight="1">
-      <c r="A15" s="280" t="s">
+      <c r="B16" s="276"/>
+      <c r="C16" s="276"/>
+      <c r="D16" s="276"/>
+      <c r="E16" s="276"/>
+      <c r="F16" s="276"/>
+      <c r="G16" s="276"/>
+      <c r="H16" s="276"/>
+      <c r="I16" s="276"/>
+      <c r="J16" s="276"/>
+      <c r="K16" s="276"/>
+      <c r="L16" s="276"/>
+      <c r="M16" s="276"/>
+      <c r="N16" s="276"/>
+      <c r="P16" s="6" t="s">
         <v>189</v>
-      </c>
-      <c r="B15" s="280"/>
-      <c r="C15" s="280"/>
-      <c r="D15" s="280"/>
-      <c r="E15" s="280"/>
-      <c r="F15" s="280"/>
-      <c r="G15" s="280"/>
-      <c r="H15" s="280"/>
-      <c r="I15" s="280"/>
-      <c r="J15" s="280"/>
-      <c r="K15" s="280"/>
-      <c r="L15" s="280"/>
-      <c r="M15" s="280"/>
-      <c r="N15" s="280"/>
-    </row>
-    <row r="16" spans="1:16">
-      <c r="A16" s="280" t="s">
-        <v>190</v>
-      </c>
-      <c r="B16" s="280"/>
-      <c r="C16" s="280"/>
-      <c r="D16" s="280"/>
-      <c r="E16" s="280"/>
-      <c r="F16" s="280"/>
-      <c r="G16" s="280"/>
-      <c r="H16" s="280"/>
-      <c r="I16" s="280"/>
-      <c r="J16" s="280"/>
-      <c r="K16" s="280"/>
-      <c r="L16" s="280"/>
-      <c r="M16" s="280"/>
-      <c r="N16" s="280"/>
-      <c r="P16" s="6" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="29.25">
       <c r="A17" s="56" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B17" s="56"/>
       <c r="C17" s="56"/>
@@ -28012,7 +27754,7 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="6" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
@@ -28054,70 +27796,70 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:13" ht="17.25">
-      <c r="A2" s="283"/>
-      <c r="B2" s="284" t="s">
+      <c r="A2" s="284"/>
+      <c r="B2" s="285" t="s">
+        <v>192</v>
+      </c>
+      <c r="C2" s="284" t="s">
+        <v>193</v>
+      </c>
+      <c r="D2" s="286" t="s">
         <v>194</v>
       </c>
-      <c r="C2" s="283" t="s">
+      <c r="E2" s="287"/>
+      <c r="F2" s="287"/>
+      <c r="G2" s="287"/>
+      <c r="H2" s="285" t="s">
         <v>195</v>
       </c>
-      <c r="D2" s="285" t="s">
+      <c r="J2" s="282" t="s">
         <v>196</v>
       </c>
-      <c r="E2" s="286"/>
-      <c r="F2" s="286"/>
-      <c r="G2" s="286"/>
-      <c r="H2" s="284" t="s">
+      <c r="K2" s="283"/>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="284"/>
+      <c r="B3" s="285"/>
+      <c r="C3" s="284"/>
+      <c r="D3" s="62" t="s">
         <v>197</v>
       </c>
-      <c r="J2" s="281" t="s">
+      <c r="E3" s="62" t="s">
         <v>198</v>
       </c>
-      <c r="K2" s="282"/>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="283"/>
-      <c r="B3" s="284"/>
-      <c r="C3" s="283"/>
-      <c r="D3" s="62" t="s">
+      <c r="F3" s="62" t="s">
         <v>199</v>
       </c>
-      <c r="E3" s="62" t="s">
+      <c r="G3" s="64" t="s">
+        <v>156</v>
+      </c>
+      <c r="H3" s="285"/>
+      <c r="J3" s="65" t="s">
         <v>200</v>
       </c>
-      <c r="F3" s="62" t="s">
+      <c r="K3" s="66" t="s">
         <v>201</v>
       </c>
-      <c r="G3" s="64" t="s">
-        <v>158</v>
-      </c>
-      <c r="H3" s="284"/>
-      <c r="J3" s="65" t="s">
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="284"/>
+      <c r="B4" s="285"/>
+      <c r="C4" s="284"/>
+      <c r="D4" s="62" t="s">
         <v>202</v>
       </c>
-      <c r="K3" s="66" t="s">
+      <c r="E4" s="62" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="283"/>
-      <c r="B4" s="284"/>
-      <c r="C4" s="283"/>
-      <c r="D4" s="62" t="s">
+      <c r="F4" s="62" t="s">
         <v>204</v>
       </c>
-      <c r="E4" s="62" t="s">
+      <c r="G4" s="64" t="s">
         <v>205</v>
       </c>
-      <c r="F4" s="62" t="s">
+      <c r="H4" s="285"/>
+      <c r="J4" s="65" t="s">
         <v>206</v>
-      </c>
-      <c r="G4" s="64" t="s">
-        <v>207</v>
-      </c>
-      <c r="H4" s="284"/>
-      <c r="J4" s="65" t="s">
-        <v>208</v>
       </c>
       <c r="K4" s="67">
         <v>1</v>
@@ -28125,7 +27867,7 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="68" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C5" s="69"/>
       <c r="D5" s="69"/>
@@ -28134,7 +27876,7 @@
       <c r="G5" s="70"/>
       <c r="H5" s="71"/>
       <c r="J5" s="65" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K5" s="67">
         <v>30</v>
@@ -28143,10 +27885,10 @@
     <row r="6" spans="1:13">
       <c r="A6" s="72"/>
       <c r="B6" s="73" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C6" s="72" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D6" s="74">
         <f>D69*$G$69*10^-6</f>
@@ -28165,11 +27907,11 @@
         <v>5.7279629999999991E-2</v>
       </c>
       <c r="H6" s="75" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I6" s="76"/>
       <c r="J6" s="65" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="K6" s="67">
         <v>28</v>
@@ -28178,10 +27920,10 @@
     <row r="7" spans="1:13">
       <c r="A7" s="72"/>
       <c r="B7" s="73" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C7" s="72" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D7" s="74">
         <f>D69/1000000</f>
@@ -28200,11 +27942,11 @@
         <v>5.6156499999999998E-2</v>
       </c>
       <c r="H7" s="75" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I7" s="76"/>
       <c r="J7" s="65" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="K7" s="67">
         <v>265</v>
@@ -28213,7 +27955,7 @@
     <row r="8" spans="1:13">
       <c r="A8" s="72"/>
       <c r="B8" s="73" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C8" s="72" t="s">
         <v>37</v>
@@ -28235,11 +27977,11 @@
         <v>1.0619459249999998</v>
       </c>
       <c r="H8" s="75" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I8" s="76"/>
       <c r="J8" s="65" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="K8" s="67">
         <v>23500</v>
@@ -28248,10 +27990,10 @@
     <row r="9" spans="1:13">
       <c r="A9" s="72"/>
       <c r="B9" s="73" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C9" s="72" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D9" s="74">
         <f>D71*$G$71*10^-6</f>
@@ -28270,11 +28012,11 @@
         <v>3.2200242184365275</v>
       </c>
       <c r="H9" s="75" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I9" s="76"/>
       <c r="J9" s="65" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K9" s="67">
         <v>16100</v>
@@ -28283,10 +28025,10 @@
     <row r="10" spans="1:13">
       <c r="A10" s="72"/>
       <c r="B10" s="73" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C10" s="72" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D10" s="74">
         <f>D72*$G$72*10^-6</f>
@@ -28305,20 +28047,20 @@
         <v>3.2457483656083648</v>
       </c>
       <c r="H10" s="75" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I10" s="76"/>
       <c r="J10" s="63" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="72"/>
       <c r="B11" s="73" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C11" s="72" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D11" s="74">
         <f>D73*$G$73*10^-6</f>
@@ -28337,14 +28079,14 @@
         <v>2.7077905800000002</v>
       </c>
       <c r="H11" s="75" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I11" s="76"/>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="72"/>
       <c r="B12" s="73" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C12" s="72" t="s">
         <v>37</v>
@@ -28366,7 +28108,7 @@
         <v>3.1000435</v>
       </c>
       <c r="H12" s="75" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I12" s="76"/>
       <c r="L12" s="77" t="s">
@@ -28376,7 +28118,7 @@
     <row r="13" spans="1:13">
       <c r="A13" s="72"/>
       <c r="B13" s="73" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C13" s="72" t="s">
         <v>37</v>
@@ -28398,14 +28140,14 @@
         <v>2.5454301749999999</v>
       </c>
       <c r="H13" s="75" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I13" s="76"/>
       <c r="J13" s="63" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="K13" s="63" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L13" s="78">
         <v>2.1019999999999999</v>
@@ -28417,10 +28159,10 @@
     <row r="14" spans="1:13">
       <c r="A14" s="72"/>
       <c r="B14" s="73" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C14" s="72" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D14" s="74">
         <f>D76*$G$76*10^-6</f>
@@ -28439,11 +28181,11 @@
         <v>2.4774929700000001</v>
       </c>
       <c r="H14" s="75" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I14" s="76"/>
       <c r="K14" s="63" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L14" s="78">
         <v>0.79479999999999995</v>
@@ -28455,10 +28197,10 @@
     <row r="15" spans="1:13">
       <c r="A15" s="72"/>
       <c r="B15" s="73" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C15" s="72" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D15" s="74">
         <f>D77*$G$77*10^-6</f>
@@ -28477,7 +28219,7 @@
         <v>1.6812260299999999</v>
       </c>
       <c r="H15" s="75" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I15" s="76"/>
       <c r="K15" s="63" t="s">
@@ -28493,7 +28235,7 @@
     <row r="16" spans="1:13">
       <c r="A16" s="68"/>
       <c r="B16" s="73" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C16" s="72" t="s">
         <v>37</v>
@@ -28515,11 +28257,11 @@
         <v>3.1133815370370366</v>
       </c>
       <c r="H16" s="75" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I16" s="76"/>
       <c r="K16" s="63" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L16" s="79">
         <v>4.3548999999999998</v>
@@ -28531,10 +28273,10 @@
     <row r="17" spans="1:9">
       <c r="A17" s="68"/>
       <c r="B17" s="73" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C17" s="72" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D17" s="74">
         <f>D78*$G$78*10^-6</f>
@@ -28553,14 +28295,14 @@
         <v>2.1894025199999998</v>
       </c>
       <c r="H17" s="75" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I17" s="76"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="68"/>
       <c r="B18" s="73" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C18" s="72" t="s">
         <v>37</v>
@@ -28579,14 +28321,14 @@
         <v>3.0380999999999998E-2</v>
       </c>
       <c r="H18" s="75" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I18" s="76"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="68"/>
       <c r="B19" s="73" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C19" s="72" t="s">
         <v>37</v>
@@ -28605,14 +28347,14 @@
         <v>1.4307E-2</v>
       </c>
       <c r="H19" s="75" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I19" s="76"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="68"/>
       <c r="B20" s="73" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C20" s="72" t="s">
         <v>37</v>
@@ -28631,14 +28373,14 @@
         <v>3.5207000000000002E-2</v>
       </c>
       <c r="H20" s="75" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I20" s="76"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="68"/>
       <c r="B21" s="73" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C21" s="72" t="s">
         <v>37</v>
@@ -28657,14 +28399,14 @@
         <v>3.1882000000000001E-2</v>
       </c>
       <c r="H21" s="75" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I21" s="76"/>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="68"/>
       <c r="B22" s="73" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C22" s="72" t="s">
         <v>57</v>
@@ -28683,14 +28425,14 @@
         <v>1.1406849999999998E-3</v>
       </c>
       <c r="H22" s="75" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I22" s="76"/>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="68"/>
       <c r="B23" s="73" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C23" s="72" t="s">
         <v>37</v>
@@ -28706,14 +28448,14 @@
         <v>1.79088</v>
       </c>
       <c r="H23" s="75" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I23" s="76"/>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="68"/>
       <c r="B24" s="73" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C24" s="72" t="s">
         <v>37</v>
@@ -28729,14 +28471,14 @@
         <v>0.753</v>
       </c>
       <c r="H24" s="75" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I24" s="76"/>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="68"/>
       <c r="B25" s="73" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C25" s="72" t="s">
         <v>37</v>
@@ -28752,14 +28494,14 @@
         <v>1.853</v>
       </c>
       <c r="H25" s="75" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I25" s="76"/>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="68"/>
       <c r="B26" s="73" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C26" s="72" t="s">
         <v>37</v>
@@ -28775,14 +28517,14 @@
         <v>1.6779999999999999</v>
       </c>
       <c r="H26" s="75" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I26" s="76"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="68"/>
       <c r="B27" s="73" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C27" s="72" t="s">
         <v>57</v>
@@ -28798,13 +28540,13 @@
         <v>1.1427779999999998</v>
       </c>
       <c r="H27" s="75" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I27" s="76"/>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="68" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B28" s="73"/>
       <c r="C28" s="72"/>
@@ -28818,10 +28560,10 @@
     <row r="29" spans="1:9">
       <c r="A29" s="68"/>
       <c r="B29" s="73" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C29" s="80" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D29" s="74">
         <f>D90*$G$90*10^-6</f>
@@ -28840,17 +28582,17 @@
         <v>2.2394242399999995</v>
       </c>
       <c r="H29" s="75" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="I29" s="76"/>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="68"/>
       <c r="B30" s="73" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C30" s="80" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D30" s="74">
         <f>D91*$G$91*10^-6</f>
@@ -28869,17 +28611,17 @@
         <v>2.2719116000000001</v>
       </c>
       <c r="H30" s="75" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="I30" s="76"/>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="68"/>
       <c r="B31" s="73" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C31" s="80" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D31" s="74">
         <f>D92*$G$92*10^-6</f>
@@ -28898,17 +28640,17 @@
         <v>2.2327032600000001</v>
       </c>
       <c r="H31" s="75" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="I31" s="76"/>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="68"/>
       <c r="B32" s="73" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C32" s="80" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D32" s="74">
         <f>D93*$G$93*10^-6</f>
@@ -28927,14 +28669,14 @@
         <v>2.7406232100000003</v>
       </c>
       <c r="H32" s="75" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="I32" s="76"/>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="68"/>
       <c r="B33" s="73" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C33" s="80" t="s">
         <v>37</v>
@@ -28956,17 +28698,17 @@
         <v>2.2609244999999998</v>
       </c>
       <c r="H33" s="75" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="I33" s="76"/>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="68"/>
       <c r="B34" s="73" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C34" s="80" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D34" s="74">
         <f>D95*$G$95*10^-6</f>
@@ -28985,14 +28727,14 @@
         <v>1.73064606</v>
       </c>
       <c r="H34" s="75" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="I34" s="76"/>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="68"/>
       <c r="B35" s="73" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C35" s="72" t="s">
         <v>37</v>
@@ -29014,13 +28756,13 @@
         <v>3.2049001111111108</v>
       </c>
       <c r="H35" s="75" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="I35" s="76"/>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="68" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B36" s="73"/>
       <c r="C36" s="72"/>
@@ -29034,7 +28776,7 @@
     <row r="37" spans="1:9">
       <c r="A37" s="68"/>
       <c r="B37" s="81" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C37" s="80"/>
       <c r="D37" s="74"/>
@@ -29047,10 +28789,10 @@
     <row r="38" spans="1:9">
       <c r="A38" s="68"/>
       <c r="B38" s="82" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C38" s="80" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D38" s="74">
         <f>D102*$G$102/(10^6)</f>
@@ -29069,17 +28811,17 @@
         <v>2.9792834700000004</v>
       </c>
       <c r="H38" s="75" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="I38" s="76"/>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" s="68"/>
       <c r="B39" s="82" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C39" s="80" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D39" s="74">
         <f>D103*$G$103/(10^6)</f>
@@ -29098,17 +28840,17 @@
         <v>2.9792834700000004</v>
       </c>
       <c r="H39" s="75" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="I39" s="76"/>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="68"/>
       <c r="B40" s="82" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C40" s="80" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D40" s="74">
         <f>D104*$G$104/(10^6)</f>
@@ -29127,17 +28869,17 @@
         <v>2.9792834700000004</v>
       </c>
       <c r="H40" s="75" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="I40" s="76"/>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" s="68"/>
       <c r="B41" s="82" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C41" s="80" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D41" s="74">
         <f>D105*$G$105/(10^6)</f>
@@ -29156,14 +28898,14 @@
         <v>2.9792834700000004</v>
       </c>
       <c r="H41" s="75" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="I41" s="76"/>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" s="68"/>
       <c r="B42" s="81" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C42" s="80"/>
       <c r="D42" s="74"/>
@@ -29176,10 +28918,10 @@
     <row r="43" spans="1:9">
       <c r="A43" s="68"/>
       <c r="B43" s="82" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C43" s="80" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D43" s="74">
         <f>D107*$G$107/(10^6)</f>
@@ -29198,17 +28940,17 @@
         <v>2.2738003999999998</v>
       </c>
       <c r="H43" s="75" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="I43" s="76"/>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" s="71"/>
       <c r="B44" s="82" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C44" s="80" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D44" s="74">
         <f>D108*$G$108/(10^6)</f>
@@ -29227,17 +28969,17 @@
         <v>2.1815639999999998</v>
       </c>
       <c r="H44" s="75" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="I44" s="76"/>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" s="71"/>
       <c r="B45" s="82" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C45" s="80" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D45" s="74">
         <f>D109*$G$109/(10^6)</f>
@@ -29256,17 +28998,17 @@
         <v>2.2454683999999996</v>
       </c>
       <c r="H45" s="75" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="I45" s="76"/>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" s="71"/>
       <c r="B46" s="82" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C46" s="80" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D46" s="74">
         <f>D110*$G$110/(10^6)</f>
@@ -29285,14 +29027,14 @@
         <v>2.3115763999999999</v>
       </c>
       <c r="H46" s="75" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="I46" s="76"/>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" s="68"/>
       <c r="B47" s="81" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C47" s="80"/>
       <c r="D47" s="74"/>
@@ -29305,10 +29047,10 @@
     <row r="48" spans="1:9">
       <c r="A48" s="68"/>
       <c r="B48" s="82" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C48" s="80" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D48" s="74">
         <f>D112*$G$112/(10^6)</f>
@@ -29327,17 +29069,17 @@
         <v>2.3171168799999999</v>
       </c>
       <c r="H48" s="75" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="I48" s="76"/>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" s="71"/>
       <c r="B49" s="82" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C49" s="80" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D49" s="74">
         <f>D113*$G$113/(10^6)</f>
@@ -29356,17 +29098,17 @@
         <v>2.3454488799999997</v>
       </c>
       <c r="H49" s="75" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="I49" s="76"/>
     </row>
     <row r="50" spans="1:10">
       <c r="A50" s="71"/>
       <c r="B50" s="82" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C50" s="80" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D50" s="74">
         <f>D114*$G$114/(10^6)</f>
@@ -29385,17 +29127,17 @@
         <v>2.3076728799999997</v>
       </c>
       <c r="H50" s="75" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="I50" s="76"/>
     </row>
     <row r="51" spans="1:10">
       <c r="A51" s="71"/>
       <c r="B51" s="82" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C51" s="80" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D51" s="74">
         <f>D115*$G$115/(10^6)</f>
@@ -29414,13 +29156,13 @@
         <v>2.35489288</v>
       </c>
       <c r="H51" s="75" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="I51" s="76"/>
     </row>
     <row r="52" spans="1:10">
       <c r="A52" s="68" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B52" s="82"/>
       <c r="C52" s="80"/>
@@ -29434,32 +29176,32 @@
     <row r="53" spans="1:10" ht="42.75">
       <c r="A53" s="83"/>
       <c r="B53" s="84" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C53" s="75" t="s">
         <v>51</v>
       </c>
       <c r="D53" s="74" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E53" s="74" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F53" s="74" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G53" s="70">
         <v>0.49990000000000001</v>
       </c>
       <c r="H53" s="85" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="I53" s="76"/>
       <c r="J53" s="86"/>
     </row>
     <row r="54" spans="1:10">
       <c r="A54" s="87" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B54" s="84"/>
       <c r="C54" s="75"/>
@@ -29473,175 +29215,175 @@
     <row r="55" spans="1:10">
       <c r="A55" s="87"/>
       <c r="B55" s="84" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C55" s="75" t="s">
         <v>37</v>
       </c>
       <c r="D55" s="74" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E55" s="74" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F55" s="74" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G55" s="70">
         <v>1760</v>
       </c>
       <c r="H55" s="85" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="I55" s="76"/>
     </row>
     <row r="56" spans="1:10">
       <c r="A56" s="83"/>
       <c r="B56" s="84" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C56" s="75" t="s">
         <v>37</v>
       </c>
       <c r="D56" s="74" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E56" s="74" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F56" s="74" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G56" s="70">
         <v>677</v>
       </c>
       <c r="H56" s="85" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="I56" s="76"/>
     </row>
     <row r="57" spans="1:10">
       <c r="A57" s="83"/>
       <c r="B57" s="84" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C57" s="75" t="s">
         <v>37</v>
       </c>
       <c r="D57" s="74" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E57" s="74" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F57" s="74" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G57" s="70">
         <v>3170</v>
       </c>
       <c r="H57" s="85" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="I57" s="76"/>
     </row>
     <row r="58" spans="1:10">
       <c r="A58" s="83"/>
       <c r="B58" s="84" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C58" s="75" t="s">
         <v>37</v>
       </c>
       <c r="D58" s="74" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E58" s="74" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F58" s="74" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G58" s="70">
         <v>1120</v>
       </c>
       <c r="H58" s="85" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="I58" s="76"/>
     </row>
     <row r="59" spans="1:10">
       <c r="A59" s="83"/>
       <c r="B59" s="84" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C59" s="75" t="s">
         <v>37</v>
       </c>
       <c r="D59" s="74" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E59" s="74" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F59" s="74" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G59" s="70">
         <v>1300</v>
       </c>
       <c r="H59" s="85" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="I59" s="76"/>
     </row>
     <row r="60" spans="1:10">
       <c r="A60" s="83"/>
       <c r="B60" s="84" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C60" s="75" t="s">
         <v>37</v>
       </c>
       <c r="D60" s="74" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E60" s="74" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F60" s="74" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G60" s="70">
         <v>328</v>
       </c>
       <c r="H60" s="85" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="I60" s="76"/>
     </row>
     <row r="61" spans="1:10">
       <c r="A61" s="83"/>
       <c r="B61" s="84" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C61" s="75" t="s">
         <v>37</v>
       </c>
       <c r="D61" s="74" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E61" s="74" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F61" s="74" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G61" s="70">
         <v>4800</v>
       </c>
       <c r="H61" s="85" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="I61" s="76"/>
     </row>
@@ -29658,13 +29400,13 @@
     </row>
     <row r="63" spans="1:10">
       <c r="A63" s="63" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B63" s="94"/>
       <c r="C63" s="77"/>
       <c r="D63" s="91"/>
       <c r="E63" s="95" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="F63" s="91"/>
       <c r="G63" s="92"/>
@@ -29683,7 +29425,7 @@
     </row>
     <row r="65" spans="1:12" s="101" customFormat="1">
       <c r="A65" s="96" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B65" s="97"/>
       <c r="C65" s="97"/>
@@ -29695,49 +29437,49 @@
     <row r="66" spans="1:12">
       <c r="D66" s="102"/>
       <c r="E66" s="103" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F66" s="103"/>
       <c r="G66" s="104" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="67" spans="1:12" ht="14.25" customHeight="1">
       <c r="B67" s="73"/>
       <c r="C67" s="72"/>
-      <c r="D67" s="287" t="s">
-        <v>282</v>
-      </c>
-      <c r="E67" s="287"/>
-      <c r="F67" s="287"/>
+      <c r="D67" s="277" t="s">
+        <v>280</v>
+      </c>
+      <c r="E67" s="277"/>
+      <c r="F67" s="277"/>
       <c r="G67" s="106" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="68" spans="1:12">
       <c r="B68" s="73"/>
       <c r="C68" s="72" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D68" s="105" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E68" s="72" t="s">
+        <v>212</v>
+      </c>
+      <c r="F68" s="72" t="s">
         <v>214</v>
       </c>
-      <c r="F68" s="72" t="s">
-        <v>216</v>
-      </c>
       <c r="G68" s="106" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="69" spans="1:12">
       <c r="B69" s="73" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C69" s="72" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D69" s="107">
         <v>56100</v>
@@ -29752,12 +29494,12 @@
         <v>1.02</v>
       </c>
       <c r="H69" s="63" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="70" spans="1:12">
       <c r="B70" s="73" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C70" s="72" t="s">
         <v>37</v>
@@ -29777,10 +29519,10 @@
     </row>
     <row r="71" spans="1:12">
       <c r="B71" s="73" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C71" s="72" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D71" s="107">
         <v>77400</v>
@@ -29795,17 +29537,17 @@
         <v>41.468972149500026</v>
       </c>
       <c r="H71" s="63" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="K71" s="77"/>
       <c r="L71" s="109"/>
     </row>
     <row r="72" spans="1:12">
       <c r="B72" s="73" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C72" s="72" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D72" s="107">
         <v>77400</v>
@@ -29820,17 +29562,17 @@
         <v>41.800259702100021</v>
       </c>
       <c r="H72" s="63" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="K72" s="77"/>
       <c r="L72" s="109"/>
     </row>
     <row r="73" spans="1:12">
       <c r="B73" s="73" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C73" s="72" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D73" s="107">
         <v>74100</v>
@@ -29847,7 +29589,7 @@
     </row>
     <row r="74" spans="1:12">
       <c r="B74" s="73" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C74" s="72" t="s">
         <v>37</v>
@@ -29867,7 +29609,7 @@
     </row>
     <row r="75" spans="1:12">
       <c r="B75" s="110" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C75" s="108" t="s">
         <v>37</v>
@@ -29887,10 +29629,10 @@
     </row>
     <row r="76" spans="1:12">
       <c r="B76" s="73" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C76" s="72" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D76" s="107">
         <v>71500</v>
@@ -29907,10 +29649,10 @@
     </row>
     <row r="77" spans="1:12">
       <c r="B77" s="73" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C77" s="72" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D77" s="107">
         <v>63100</v>
@@ -29927,10 +29669,10 @@
     </row>
     <row r="78" spans="1:12">
       <c r="B78" s="73" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C78" s="72" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D78" s="107">
         <v>69300</v>
@@ -29948,7 +29690,7 @@
     </row>
     <row r="79" spans="1:12">
       <c r="B79" s="73" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C79" s="72" t="s">
         <v>37</v>
@@ -29968,7 +29710,7 @@
     </row>
     <row r="80" spans="1:12">
       <c r="B80" s="73" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C80" s="72"/>
       <c r="D80" s="107"/>
@@ -29978,7 +29720,7 @@
     </row>
     <row r="81" spans="1:8">
       <c r="B81" s="73" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C81" s="72" t="s">
         <v>37</v>
@@ -29998,7 +29740,7 @@
     </row>
     <row r="82" spans="1:8">
       <c r="B82" s="73" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C82" s="72" t="s">
         <v>37</v>
@@ -30018,7 +29760,7 @@
     </row>
     <row r="83" spans="1:8">
       <c r="B83" s="73" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C83" s="72" t="s">
         <v>37</v>
@@ -30038,10 +29780,10 @@
     </row>
     <row r="84" spans="1:8" ht="15.75">
       <c r="B84" s="73" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C84" s="72" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D84" s="107">
         <v>54600</v>
@@ -30064,7 +29806,7 @@
     </row>
     <row r="86" spans="1:8" s="101" customFormat="1">
       <c r="A86" s="96" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B86" s="97"/>
       <c r="C86" s="97"/>
@@ -30074,51 +29816,51 @@
       <c r="G86" s="100"/>
     </row>
     <row r="87" spans="1:8">
-      <c r="D87" s="288" t="s">
-        <v>280</v>
-      </c>
-      <c r="E87" s="288"/>
-      <c r="F87" s="288"/>
+      <c r="D87" s="278" t="s">
+        <v>278</v>
+      </c>
+      <c r="E87" s="278"/>
+      <c r="F87" s="278"/>
       <c r="G87" s="104" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="88" spans="1:8">
       <c r="B88" s="73"/>
       <c r="C88" s="71"/>
-      <c r="D88" s="289" t="s">
-        <v>282</v>
-      </c>
-      <c r="E88" s="290"/>
-      <c r="F88" s="291"/>
+      <c r="D88" s="279" t="s">
+        <v>280</v>
+      </c>
+      <c r="E88" s="280"/>
+      <c r="F88" s="281"/>
       <c r="G88" s="106" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="89" spans="1:8">
       <c r="B89" s="73"/>
       <c r="C89" s="80" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D89" s="72" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E89" s="105" t="s">
+        <v>212</v>
+      </c>
+      <c r="F89" s="72" t="s">
         <v>214</v>
       </c>
-      <c r="F89" s="72" t="s">
-        <v>216</v>
-      </c>
       <c r="G89" s="106" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="90" spans="1:8">
       <c r="B90" s="73" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C90" s="80" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D90" s="72">
         <v>69300</v>
@@ -30133,15 +29875,15 @@
         <v>31.48</v>
       </c>
       <c r="H90" s="63" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="91" spans="1:8">
       <c r="B91" s="73" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C91" s="80" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D91" s="72">
         <v>69300</v>
@@ -30158,10 +29900,10 @@
     </row>
     <row r="92" spans="1:8">
       <c r="B92" s="73" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C92" s="80" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D92" s="72">
         <v>69300</v>
@@ -30178,10 +29920,10 @@
     </row>
     <row r="93" spans="1:8">
       <c r="B93" s="73" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C93" s="80" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D93" s="72">
         <v>74100</v>
@@ -30199,7 +29941,7 @@
     </row>
     <row r="94" spans="1:8">
       <c r="B94" s="73" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C94" s="80" t="s">
         <v>37</v>
@@ -30217,15 +29959,15 @@
         <v>37.9</v>
       </c>
       <c r="H94" s="63" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="95" spans="1:8">
       <c r="B95" s="73" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C95" s="80" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D95" s="72">
         <v>63100</v>
@@ -30248,7 +29990,7 @@
     </row>
     <row r="97" spans="1:7" s="101" customFormat="1">
       <c r="A97" s="96" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B97" s="97"/>
       <c r="C97" s="97"/>
@@ -30258,48 +30000,48 @@
       <c r="G97" s="100"/>
     </row>
     <row r="98" spans="1:7">
-      <c r="D98" s="288" t="s">
-        <v>280</v>
-      </c>
-      <c r="E98" s="288"/>
-      <c r="F98" s="288"/>
+      <c r="D98" s="278" t="s">
+        <v>278</v>
+      </c>
+      <c r="E98" s="278"/>
+      <c r="F98" s="278"/>
       <c r="G98" s="104" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="99" spans="1:7">
       <c r="B99" s="73"/>
       <c r="C99" s="71"/>
-      <c r="D99" s="289" t="s">
-        <v>282</v>
-      </c>
-      <c r="E99" s="290"/>
-      <c r="F99" s="291"/>
+      <c r="D99" s="279" t="s">
+        <v>280</v>
+      </c>
+      <c r="E99" s="280"/>
+      <c r="F99" s="281"/>
       <c r="G99" s="106" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="100" spans="1:7">
       <c r="B100" s="73"/>
       <c r="C100" s="80" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D100" s="72" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E100" s="105" t="s">
+        <v>212</v>
+      </c>
+      <c r="F100" s="72" t="s">
         <v>214</v>
       </c>
-      <c r="F100" s="72" t="s">
-        <v>216</v>
-      </c>
       <c r="G100" s="106" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="101" spans="1:7">
       <c r="B101" s="81" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C101" s="80"/>
       <c r="D101" s="72"/>
@@ -30309,10 +30051,10 @@
     </row>
     <row r="102" spans="1:7">
       <c r="B102" s="82" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C102" s="80" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D102" s="72">
         <v>74100</v>
@@ -30329,10 +30071,10 @@
     </row>
     <row r="103" spans="1:7">
       <c r="B103" s="82" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C103" s="80" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D103" s="72">
         <v>74100</v>
@@ -30349,10 +30091,10 @@
     </row>
     <row r="104" spans="1:7">
       <c r="B104" s="82" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C104" s="80" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D104" s="72">
         <v>74100</v>
@@ -30369,10 +30111,10 @@
     </row>
     <row r="105" spans="1:7">
       <c r="B105" s="82" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C105" s="80" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D105" s="72">
         <v>74100</v>
@@ -30389,7 +30131,7 @@
     </row>
     <row r="106" spans="1:7">
       <c r="B106" s="81" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C106" s="80"/>
       <c r="D106" s="72"/>
@@ -30399,10 +30141,10 @@
     </row>
     <row r="107" spans="1:7">
       <c r="B107" s="82" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C107" s="80" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D107" s="112">
         <v>69300</v>
@@ -30419,10 +30161,10 @@
     </row>
     <row r="108" spans="1:7">
       <c r="B108" s="82" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C108" s="80" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D108" s="112">
         <v>69300</v>
@@ -30435,10 +30177,10 @@
     </row>
     <row r="109" spans="1:7">
       <c r="B109" s="82" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C109" s="80" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D109" s="112">
         <v>69300</v>
@@ -30455,10 +30197,10 @@
     </row>
     <row r="110" spans="1:7">
       <c r="B110" s="82" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C110" s="80" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D110" s="112">
         <v>69300</v>
@@ -30475,7 +30217,7 @@
     </row>
     <row r="111" spans="1:7">
       <c r="B111" s="81" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C111" s="71"/>
       <c r="D111" s="113"/>
@@ -30485,10 +30227,10 @@
     </row>
     <row r="112" spans="1:7">
       <c r="B112" s="82" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C112" s="80" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D112" s="112">
         <v>69300</v>
@@ -30505,10 +30247,10 @@
     </row>
     <row r="113" spans="2:7">
       <c r="B113" s="82" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C113" s="80" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D113" s="112">
         <v>69300</v>
@@ -30525,10 +30267,10 @@
     </row>
     <row r="114" spans="2:7">
       <c r="B114" s="82" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C114" s="80" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D114" s="112">
         <v>69300</v>
@@ -30545,10 +30287,10 @@
     </row>
     <row r="115" spans="2:7">
       <c r="B115" s="82" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C115" s="80" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D115" s="112">
         <v>69300</v>
@@ -30910,17 +30652,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="D87:F87"/>
-    <mergeCell ref="D88:F88"/>
-    <mergeCell ref="D98:F98"/>
-    <mergeCell ref="D99:F99"/>
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="C2:C4"/>
     <mergeCell ref="D2:G2"/>
     <mergeCell ref="H2:H4"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="D87:F87"/>
+    <mergeCell ref="D88:F88"/>
+    <mergeCell ref="D98:F98"/>
+    <mergeCell ref="D99:F99"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E63" r:id="rId1" xr:uid="{DB1ADA9E-3F35-4845-AAD6-B0CDE56A2D4E}"/>
@@ -30931,6 +30673,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FB289CDA5892614FBD5176687F996656" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="224aee30ab98573123b2948b9eb4fbbf">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="7b8fd10d-82db-4106-8c5b-83cd3e4ad2c7" xmlns:ns4="abcb2651-95fa-414f-a10c-971ab93c7c80" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="35e8a1d91f3affbad42a72f8f9e048d5" ns3:_="" ns4:_="">
     <xsd:import namespace="7b8fd10d-82db-4106-8c5b-83cd3e4ad2c7"/>
@@ -31171,15 +30922,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -31189,11 +30931,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9EB2AE26-E6D0-4F6B-8269-CB6F368CF6C9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7B1A4E4-5374-4A28-AFAE-9E2859F6DF47}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7B1A4E4-5374-4A28-AFAE-9E2859F6DF47}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9EB2AE26-E6D0-4F6B-8269-CB6F368CF6C9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
